--- a/knowledge_base/ciq_fetches/CIQ_Fetch_Template.xlsx
+++ b/knowledge_base/ciq_fetches/CIQ_Fetch_Template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,18 @@
       <color rgb="00444444"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="000000CC"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
@@ -50,10 +62,6 @@
     <font>
       <b val="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <color rgb="000000CC"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -97,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -105,12 +113,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -516,8034 +527,8054 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Filing currency (helper):</t>
+        </is>
+      </c>
+      <c r="C3" s="6">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_FILING_CURRENCY")</f>
+        <v/>
+      </c>
+      <c r="D3" s="7">
+        <f>C3</f>
+        <v/>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>ISO 4217 code (e.g. USD, HKD, CNY). Referenced by _reporting formulas.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>CIQ Formula</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Resolved Value</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>INCOME STATEMENT (Annual)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FY-0")</f>
         <v/>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="12">
         <f>C6</f>
         <v/>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FY-1")</f>
         <v/>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="12">
         <f>C7</f>
         <v/>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FY-2")</f>
         <v/>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="12">
         <f>C8</f>
         <v/>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FY-3")</f>
         <v/>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="12">
         <f>C9</f>
         <v/>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FY-4")</f>
         <v/>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="12">
         <f>C10</f>
         <v/>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FY-5")</f>
         <v/>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="12">
         <f>C11</f>
         <v/>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FY-6")</f>
         <v/>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="12">
         <f>C12</f>
         <v/>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FY-7")</f>
         <v/>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="12">
         <f>C13</f>
         <v/>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FY-8")</f>
         <v/>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="12">
         <f>C14</f>
         <v/>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FY-9")</f>
         <v/>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="12">
         <f>C15</f>
         <v/>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FY-10")</f>
         <v/>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="12">
         <f>C16</f>
         <v/>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FY-0")</f>
         <v/>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="12">
         <f>C17</f>
         <v/>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FY-1")</f>
         <v/>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="12">
         <f>C18</f>
         <v/>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FY-2")</f>
         <v/>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="12">
         <f>C19</f>
         <v/>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FY-3")</f>
         <v/>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="12">
         <f>C20</f>
         <v/>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FY-4")</f>
         <v/>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="12">
         <f>C21</f>
         <v/>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FY-5")</f>
         <v/>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="12">
         <f>C22</f>
         <v/>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FY-6")</f>
         <v/>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="12">
         <f>C23</f>
         <v/>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FY-7")</f>
         <v/>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="12">
         <f>C24</f>
         <v/>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FY-8")</f>
         <v/>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="12">
         <f>C25</f>
         <v/>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C26" s="8">
+      <c r="C26" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FY-9")</f>
         <v/>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="12">
         <f>C26</f>
         <v/>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C27" s="8">
+      <c r="C27" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FY-10")</f>
         <v/>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="12">
         <f>C27</f>
         <v/>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C28" s="8">
+      <c r="C28" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FY-0")</f>
         <v/>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="12">
         <f>C28</f>
         <v/>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FY-1")</f>
         <v/>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="12">
         <f>C29</f>
         <v/>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FY-2")</f>
         <v/>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="12">
         <f>C30</f>
         <v/>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FY-3")</f>
         <v/>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="12">
         <f>C31</f>
         <v/>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FY-4")</f>
         <v/>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="12">
         <f>C32</f>
         <v/>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FY-5")</f>
         <v/>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="12">
         <f>C33</f>
         <v/>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C34" s="8">
+      <c r="C34" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FY-6")</f>
         <v/>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="12">
         <f>C34</f>
         <v/>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FY-7")</f>
         <v/>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="12">
         <f>C35</f>
         <v/>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FY-8")</f>
         <v/>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="12">
         <f>C36</f>
         <v/>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FY-9")</f>
         <v/>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="12">
         <f>C37</f>
         <v/>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FY-10")</f>
         <v/>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="12">
         <f>C38</f>
         <v/>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C39" s="8">
+      <c r="C39" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FY-0")</f>
         <v/>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="12">
         <f>C39</f>
         <v/>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C40" s="8">
+      <c r="C40" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FY-1")</f>
         <v/>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="12">
         <f>C40</f>
         <v/>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C41" s="8">
+      <c r="C41" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FY-2")</f>
         <v/>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="12">
         <f>C41</f>
         <v/>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C42" s="8">
+      <c r="C42" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FY-3")</f>
         <v/>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="12">
         <f>C42</f>
         <v/>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C43" s="8">
+      <c r="C43" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FY-4")</f>
         <v/>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="12">
         <f>C43</f>
         <v/>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C44" s="8">
+      <c r="C44" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FY-5")</f>
         <v/>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="12">
         <f>C44</f>
         <v/>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C45" s="8">
+      <c r="C45" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FY-6")</f>
         <v/>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="12">
         <f>C45</f>
         <v/>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C46" s="8">
+      <c r="C46" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FY-7")</f>
         <v/>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="12">
         <f>C46</f>
         <v/>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C47" s="8">
+      <c r="C47" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FY-8")</f>
         <v/>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="12">
         <f>C47</f>
         <v/>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C48" s="8">
+      <c r="C48" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FY-9")</f>
         <v/>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="12">
         <f>C48</f>
         <v/>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E48" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C49" s="8">
+      <c r="C49" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FY-10")</f>
         <v/>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="12">
         <f>C49</f>
         <v/>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E49" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C50" s="8">
+      <c r="C50" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FY-0"))</f>
         <v/>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="12">
         <f>C50</f>
         <v/>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E50" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C51" s="8">
+      <c r="C51" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FY-1"))</f>
         <v/>
       </c>
-      <c r="D51" s="9">
+      <c r="D51" s="12">
         <f>C51</f>
         <v/>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C52" s="8">
+      <c r="C52" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FY-2"))</f>
         <v/>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="12">
         <f>C52</f>
         <v/>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C53" s="8">
+      <c r="C53" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FY-3"))</f>
         <v/>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="12">
         <f>C53</f>
         <v/>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E53" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C54" s="8">
+      <c r="C54" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FY-4"))</f>
         <v/>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="12">
         <f>C54</f>
         <v/>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E54" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C55" s="8">
+      <c r="C55" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FY-5"))</f>
         <v/>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="12">
         <f>C55</f>
         <v/>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C56" s="8">
+      <c r="C56" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FY-6"))</f>
         <v/>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="12">
         <f>C56</f>
         <v/>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E56" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C57" s="8">
+      <c r="C57" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FY-7"))</f>
         <v/>
       </c>
-      <c r="D57" s="9">
+      <c r="D57" s="12">
         <f>C57</f>
         <v/>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E57" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C58" s="8">
+      <c r="C58" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FY-8"))</f>
         <v/>
       </c>
-      <c r="D58" s="9">
+      <c r="D58" s="12">
         <f>C58</f>
         <v/>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E58" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C59" s="8">
+      <c r="C59" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FY-9"))</f>
         <v/>
       </c>
-      <c r="D59" s="9">
+      <c r="D59" s="12">
         <f>C59</f>
         <v/>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E59" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C60" s="8">
+      <c r="C60" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FY-10"))</f>
         <v/>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="12">
         <f>C60</f>
         <v/>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E60" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C61" s="8">
+      <c r="C61" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FY-0"))</f>
         <v/>
       </c>
-      <c r="D61" s="9">
+      <c r="D61" s="12">
         <f>C61</f>
         <v/>
       </c>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="E61" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C62" s="8">
+      <c r="C62" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FY-1"))</f>
         <v/>
       </c>
-      <c r="D62" s="9">
+      <c r="D62" s="12">
         <f>C62</f>
         <v/>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E62" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C63" s="8">
+      <c r="C63" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FY-2"))</f>
         <v/>
       </c>
-      <c r="D63" s="9">
+      <c r="D63" s="12">
         <f>C63</f>
         <v/>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C64" s="8">
+      <c r="C64" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FY-3"))</f>
         <v/>
       </c>
-      <c r="D64" s="9">
+      <c r="D64" s="12">
         <f>C64</f>
         <v/>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E64" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C65" s="8">
+      <c r="C65" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FY-4"))</f>
         <v/>
       </c>
-      <c r="D65" s="9">
+      <c r="D65" s="12">
         <f>C65</f>
         <v/>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C66" s="8">
+      <c r="C66" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FY-5"))</f>
         <v/>
       </c>
-      <c r="D66" s="9">
+      <c r="D66" s="12">
         <f>C66</f>
         <v/>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E66" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C67" s="8">
+      <c r="C67" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FY-6"))</f>
         <v/>
       </c>
-      <c r="D67" s="9">
+      <c r="D67" s="12">
         <f>C67</f>
         <v/>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C68" s="8">
+      <c r="C68" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FY-7"))</f>
         <v/>
       </c>
-      <c r="D68" s="9">
+      <c r="D68" s="12">
         <f>C68</f>
         <v/>
       </c>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="E68" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C69" s="8">
+      <c r="C69" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FY-8"))</f>
         <v/>
       </c>
-      <c r="D69" s="9">
+      <c r="D69" s="12">
         <f>C69</f>
         <v/>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E69" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="inlineStr">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B70" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C70" s="8">
+      <c r="C70" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FY-9"))</f>
         <v/>
       </c>
-      <c r="D70" s="9">
+      <c r="D70" s="12">
         <f>C70</f>
         <v/>
       </c>
-      <c r="E70" s="7" t="inlineStr">
+      <c r="E70" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="inlineStr">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C71" s="8">
+      <c r="C71" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FY-10"))</f>
         <v/>
       </c>
-      <c r="D71" s="9">
+      <c r="D71" s="12">
         <f>C71</f>
         <v/>
       </c>
-      <c r="E71" s="7" t="inlineStr">
+      <c r="E71" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B72" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C72" s="8">
+      <c r="C72" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FY-0")</f>
         <v/>
       </c>
-      <c r="D72" s="9">
+      <c r="D72" s="12">
         <f>C72</f>
         <v/>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="E72" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="7" t="inlineStr">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B73" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C73" s="8">
+      <c r="C73" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FY-1")</f>
         <v/>
       </c>
-      <c r="D73" s="9">
+      <c r="D73" s="12">
         <f>C73</f>
         <v/>
       </c>
-      <c r="E73" s="7" t="inlineStr">
+      <c r="E73" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="inlineStr">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C74" s="8">
+      <c r="C74" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FY-2")</f>
         <v/>
       </c>
-      <c r="D74" s="9">
+      <c r="D74" s="12">
         <f>C74</f>
         <v/>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E74" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="7" t="inlineStr">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C75" s="8">
+      <c r="C75" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FY-3")</f>
         <v/>
       </c>
-      <c r="D75" s="9">
+      <c r="D75" s="12">
         <f>C75</f>
         <v/>
       </c>
-      <c r="E75" s="7" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="7" t="inlineStr">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C76" s="8">
+      <c r="C76" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FY-4")</f>
         <v/>
       </c>
-      <c r="D76" s="9">
+      <c r="D76" s="12">
         <f>C76</f>
         <v/>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E76" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="7" t="inlineStr">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B77" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C77" s="8">
+      <c r="C77" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FY-5")</f>
         <v/>
       </c>
-      <c r="D77" s="9">
+      <c r="D77" s="12">
         <f>C77</f>
         <v/>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E77" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="inlineStr">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C78" s="8">
+      <c r="C78" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FY-6")</f>
         <v/>
       </c>
-      <c r="D78" s="9">
+      <c r="D78" s="12">
         <f>C78</f>
         <v/>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E78" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="7" t="inlineStr">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B79" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C79" s="8">
+      <c r="C79" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FY-7")</f>
         <v/>
       </c>
-      <c r="D79" s="9">
+      <c r="D79" s="12">
         <f>C79</f>
         <v/>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E79" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="7" t="inlineStr">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B80" s="7" t="inlineStr">
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C80" s="8">
+      <c r="C80" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FY-8")</f>
         <v/>
       </c>
-      <c r="D80" s="9">
+      <c r="D80" s="12">
         <f>C80</f>
         <v/>
       </c>
-      <c r="E80" s="7" t="inlineStr">
+      <c r="E80" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="7" t="inlineStr">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B81" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C81" s="8">
+      <c r="C81" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FY-9")</f>
         <v/>
       </c>
-      <c r="D81" s="9">
+      <c r="D81" s="12">
         <f>C81</f>
         <v/>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E81" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="7" t="inlineStr">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C82" s="8">
+      <c r="C82" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FY-10")</f>
         <v/>
       </c>
-      <c r="D82" s="9">
+      <c r="D82" s="12">
         <f>C82</f>
         <v/>
       </c>
-      <c r="E82" s="7" t="inlineStr">
+      <c r="E82" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="7" t="inlineStr">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C83" s="8">
+      <c r="C83" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FY-0")</f>
         <v/>
       </c>
-      <c r="D83" s="9">
+      <c r="D83" s="12">
         <f>C83</f>
         <v/>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E83" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="7" t="inlineStr">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C84" s="8">
+      <c r="C84" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FY-1")</f>
         <v/>
       </c>
-      <c r="D84" s="9">
+      <c r="D84" s="12">
         <f>C84</f>
         <v/>
       </c>
-      <c r="E84" s="7" t="inlineStr">
+      <c r="E84" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="7" t="inlineStr">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C85" s="8">
+      <c r="C85" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FY-2")</f>
         <v/>
       </c>
-      <c r="D85" s="9">
+      <c r="D85" s="12">
         <f>C85</f>
         <v/>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E85" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="7" t="inlineStr">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C86" s="8">
+      <c r="C86" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FY-3")</f>
         <v/>
       </c>
-      <c r="D86" s="9">
+      <c r="D86" s="12">
         <f>C86</f>
         <v/>
       </c>
-      <c r="E86" s="7" t="inlineStr">
+      <c r="E86" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="7" t="inlineStr">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B87" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C87" s="8">
+      <c r="C87" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FY-4")</f>
         <v/>
       </c>
-      <c r="D87" s="9">
+      <c r="D87" s="12">
         <f>C87</f>
         <v/>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E87" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="7" t="inlineStr">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C88" s="8">
+      <c r="C88" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FY-5")</f>
         <v/>
       </c>
-      <c r="D88" s="9">
+      <c r="D88" s="12">
         <f>C88</f>
         <v/>
       </c>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="E88" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="7" t="inlineStr">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B89" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C89" s="8">
+      <c r="C89" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FY-6")</f>
         <v/>
       </c>
-      <c r="D89" s="9">
+      <c r="D89" s="12">
         <f>C89</f>
         <v/>
       </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="E89" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="7" t="inlineStr">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B90" s="7" t="inlineStr">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C90" s="8">
+      <c r="C90" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FY-7")</f>
         <v/>
       </c>
-      <c r="D90" s="9">
+      <c r="D90" s="12">
         <f>C90</f>
         <v/>
       </c>
-      <c r="E90" s="7" t="inlineStr">
+      <c r="E90" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="7" t="inlineStr">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="B91" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C91" s="8">
+      <c r="C91" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FY-8")</f>
         <v/>
       </c>
-      <c r="D91" s="9">
+      <c r="D91" s="12">
         <f>C91</f>
         <v/>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="E91" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="7" t="inlineStr">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C92" s="8">
+      <c r="C92" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FY-9")</f>
         <v/>
       </c>
-      <c r="D92" s="9">
+      <c r="D92" s="12">
         <f>C92</f>
         <v/>
       </c>
-      <c r="E92" s="7" t="inlineStr">
+      <c r="E92" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="7" t="inlineStr">
+      <c r="A93" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B93" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C93" s="8">
+      <c r="C93" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FY-10")</f>
         <v/>
       </c>
-      <c r="D93" s="9">
+      <c r="D93" s="12">
         <f>C93</f>
         <v/>
       </c>
-      <c r="E93" s="7" t="inlineStr">
+      <c r="E93" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="7" t="inlineStr">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C94" s="8">
+      <c r="C94" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FY-0"))</f>
         <v/>
       </c>
-      <c r="D94" s="9">
+      <c r="D94" s="12">
         <f>C94</f>
         <v/>
       </c>
-      <c r="E94" s="7" t="inlineStr">
+      <c r="E94" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="7" t="inlineStr">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B95" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C95" s="8">
+      <c r="C95" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FY-1"))</f>
         <v/>
       </c>
-      <c r="D95" s="9">
+      <c r="D95" s="12">
         <f>C95</f>
         <v/>
       </c>
-      <c r="E95" s="7" t="inlineStr">
+      <c r="E95" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="7" t="inlineStr">
+      <c r="A96" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B96" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C96" s="8">
+      <c r="C96" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FY-2"))</f>
         <v/>
       </c>
-      <c r="D96" s="9">
+      <c r="D96" s="12">
         <f>C96</f>
         <v/>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E96" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="7" t="inlineStr">
+      <c r="A97" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="B97" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C97" s="8">
+      <c r="C97" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FY-3"))</f>
         <v/>
       </c>
-      <c r="D97" s="9">
+      <c r="D97" s="12">
         <f>C97</f>
         <v/>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="E97" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="7" t="inlineStr">
+      <c r="A98" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B98" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C98" s="8">
+      <c r="C98" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FY-4"))</f>
         <v/>
       </c>
-      <c r="D98" s="9">
+      <c r="D98" s="12">
         <f>C98</f>
         <v/>
       </c>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="E98" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="7" t="inlineStr">
+      <c r="A99" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B99" s="7" t="inlineStr">
+      <c r="B99" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C99" s="8">
+      <c r="C99" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FY-5"))</f>
         <v/>
       </c>
-      <c r="D99" s="9">
+      <c r="D99" s="12">
         <f>C99</f>
         <v/>
       </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="E99" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="7" t="inlineStr">
+      <c r="A100" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B100" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C100" s="8">
+      <c r="C100" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FY-6"))</f>
         <v/>
       </c>
-      <c r="D100" s="9">
+      <c r="D100" s="12">
         <f>C100</f>
         <v/>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="E100" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="7" t="inlineStr">
+      <c r="A101" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B101" s="7" t="inlineStr">
+      <c r="B101" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C101" s="8">
+      <c r="C101" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FY-7"))</f>
         <v/>
       </c>
-      <c r="D101" s="9">
+      <c r="D101" s="12">
         <f>C101</f>
         <v/>
       </c>
-      <c r="E101" s="7" t="inlineStr">
+      <c r="E101" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="7" t="inlineStr">
+      <c r="A102" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B102" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C102" s="8">
+      <c r="C102" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FY-8"))</f>
         <v/>
       </c>
-      <c r="D102" s="9">
+      <c r="D102" s="12">
         <f>C102</f>
         <v/>
       </c>
-      <c r="E102" s="7" t="inlineStr">
+      <c r="E102" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="7" t="inlineStr">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B103" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C103" s="8">
+      <c r="C103" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FY-9"))</f>
         <v/>
       </c>
-      <c r="D103" s="9">
+      <c r="D103" s="12">
         <f>C103</f>
         <v/>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="E103" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="7" t="inlineStr">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="B104" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C104" s="8">
+      <c r="C104" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FY-10"))</f>
         <v/>
       </c>
-      <c r="D104" s="9">
+      <c r="D104" s="12">
         <f>C104</f>
         <v/>
       </c>
-      <c r="E104" s="7" t="inlineStr">
+      <c r="E104" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="7" t="inlineStr">
+      <c r="A105" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B105" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C105" s="8">
+      <c r="C105" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FY-0"))</f>
         <v/>
       </c>
-      <c r="D105" s="9">
+      <c r="D105" s="12">
         <f>C105</f>
         <v/>
       </c>
-      <c r="E105" s="7" t="inlineStr">
+      <c r="E105" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="7" t="inlineStr">
+      <c r="A106" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B106" s="7" t="inlineStr">
+      <c r="B106" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C106" s="8">
+      <c r="C106" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FY-1"))</f>
         <v/>
       </c>
-      <c r="D106" s="9">
+      <c r="D106" s="12">
         <f>C106</f>
         <v/>
       </c>
-      <c r="E106" s="7" t="inlineStr">
+      <c r="E106" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="7" t="inlineStr">
+      <c r="A107" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B107" s="7" t="inlineStr">
+      <c r="B107" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C107" s="8">
+      <c r="C107" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FY-2"))</f>
         <v/>
       </c>
-      <c r="D107" s="9">
+      <c r="D107" s="12">
         <f>C107</f>
         <v/>
       </c>
-      <c r="E107" s="7" t="inlineStr">
+      <c r="E107" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="7" t="inlineStr">
+      <c r="A108" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B108" s="7" t="inlineStr">
+      <c r="B108" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C108" s="8">
+      <c r="C108" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FY-3"))</f>
         <v/>
       </c>
-      <c r="D108" s="9">
+      <c r="D108" s="12">
         <f>C108</f>
         <v/>
       </c>
-      <c r="E108" s="7" t="inlineStr">
+      <c r="E108" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="7" t="inlineStr">
+      <c r="A109" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="B109" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C109" s="8">
+      <c r="C109" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FY-4"))</f>
         <v/>
       </c>
-      <c r="D109" s="9">
+      <c r="D109" s="12">
         <f>C109</f>
         <v/>
       </c>
-      <c r="E109" s="7" t="inlineStr">
+      <c r="E109" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="7" t="inlineStr">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B110" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C110" s="8">
+      <c r="C110" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FY-5"))</f>
         <v/>
       </c>
-      <c r="D110" s="9">
+      <c r="D110" s="12">
         <f>C110</f>
         <v/>
       </c>
-      <c r="E110" s="7" t="inlineStr">
+      <c r="E110" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="7" t="inlineStr">
+      <c r="A111" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B111" s="7" t="inlineStr">
+      <c r="B111" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C111" s="8">
+      <c r="C111" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FY-6"))</f>
         <v/>
       </c>
-      <c r="D111" s="9">
+      <c r="D111" s="12">
         <f>C111</f>
         <v/>
       </c>
-      <c r="E111" s="7" t="inlineStr">
+      <c r="E111" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="7" t="inlineStr">
+      <c r="A112" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B112" s="7" t="inlineStr">
+      <c r="B112" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C112" s="8">
+      <c r="C112" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FY-7"))</f>
         <v/>
       </c>
-      <c r="D112" s="9">
+      <c r="D112" s="12">
         <f>C112</f>
         <v/>
       </c>
-      <c r="E112" s="7" t="inlineStr">
+      <c r="E112" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="7" t="inlineStr">
+      <c r="A113" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B113" s="7" t="inlineStr">
+      <c r="B113" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C113" s="8">
+      <c r="C113" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FY-8"))</f>
         <v/>
       </c>
-      <c r="D113" s="9">
+      <c r="D113" s="12">
         <f>C113</f>
         <v/>
       </c>
-      <c r="E113" s="7" t="inlineStr">
+      <c r="E113" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="7" t="inlineStr">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B114" s="7" t="inlineStr">
+      <c r="B114" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C114" s="8">
+      <c r="C114" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FY-9"))</f>
         <v/>
       </c>
-      <c r="D114" s="9">
+      <c r="D114" s="12">
         <f>C114</f>
         <v/>
       </c>
-      <c r="E114" s="7" t="inlineStr">
+      <c r="E114" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="7" t="inlineStr">
+      <c r="A115" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B115" s="7" t="inlineStr">
+      <c r="B115" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C115" s="8">
+      <c r="C115" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FY-10"))</f>
         <v/>
       </c>
-      <c r="D115" s="9">
+      <c r="D115" s="12">
         <f>C115</f>
         <v/>
       </c>
-      <c r="E115" s="7" t="inlineStr">
+      <c r="E115" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="7" t="inlineStr">
+      <c r="A116" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B116" s="7" t="inlineStr">
+      <c r="B116" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C116" s="8">
+      <c r="C116" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FY-0")</f>
         <v/>
       </c>
-      <c r="D116" s="9">
+      <c r="D116" s="12">
         <f>C116</f>
         <v/>
       </c>
-      <c r="E116" s="7" t="inlineStr">
+      <c r="E116" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="7" t="inlineStr">
+      <c r="A117" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B117" s="7" t="inlineStr">
+      <c r="B117" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C117" s="8">
+      <c r="C117" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FY-1")</f>
         <v/>
       </c>
-      <c r="D117" s="9">
+      <c r="D117" s="12">
         <f>C117</f>
         <v/>
       </c>
-      <c r="E117" s="7" t="inlineStr">
+      <c r="E117" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="7" t="inlineStr">
+      <c r="A118" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="B118" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C118" s="8">
+      <c r="C118" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FY-2")</f>
         <v/>
       </c>
-      <c r="D118" s="9">
+      <c r="D118" s="12">
         <f>C118</f>
         <v/>
       </c>
-      <c r="E118" s="7" t="inlineStr">
+      <c r="E118" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="7" t="inlineStr">
+      <c r="A119" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B119" s="7" t="inlineStr">
+      <c r="B119" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C119" s="8">
+      <c r="C119" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FY-3")</f>
         <v/>
       </c>
-      <c r="D119" s="9">
+      <c r="D119" s="12">
         <f>C119</f>
         <v/>
       </c>
-      <c r="E119" s="7" t="inlineStr">
+      <c r="E119" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="7" t="inlineStr">
+      <c r="A120" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B120" s="7" t="inlineStr">
+      <c r="B120" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C120" s="8">
+      <c r="C120" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FY-4")</f>
         <v/>
       </c>
-      <c r="D120" s="9">
+      <c r="D120" s="12">
         <f>C120</f>
         <v/>
       </c>
-      <c r="E120" s="7" t="inlineStr">
+      <c r="E120" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="7" t="inlineStr">
+      <c r="A121" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B121" s="7" t="inlineStr">
+      <c r="B121" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C121" s="8">
+      <c r="C121" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FY-5")</f>
         <v/>
       </c>
-      <c r="D121" s="9">
+      <c r="D121" s="12">
         <f>C121</f>
         <v/>
       </c>
-      <c r="E121" s="7" t="inlineStr">
+      <c r="E121" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="7" t="inlineStr">
+      <c r="A122" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B122" s="7" t="inlineStr">
+      <c r="B122" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C122" s="8">
+      <c r="C122" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FY-6")</f>
         <v/>
       </c>
-      <c r="D122" s="9">
+      <c r="D122" s="12">
         <f>C122</f>
         <v/>
       </c>
-      <c r="E122" s="7" t="inlineStr">
+      <c r="E122" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="7" t="inlineStr">
+      <c r="A123" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B123" s="7" t="inlineStr">
+      <c r="B123" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C123" s="8">
+      <c r="C123" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FY-7")</f>
         <v/>
       </c>
-      <c r="D123" s="9">
+      <c r="D123" s="12">
         <f>C123</f>
         <v/>
       </c>
-      <c r="E123" s="7" t="inlineStr">
+      <c r="E123" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="7" t="inlineStr">
+      <c r="A124" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B124" s="7" t="inlineStr">
+      <c r="B124" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C124" s="8">
+      <c r="C124" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FY-8")</f>
         <v/>
       </c>
-      <c r="D124" s="9">
+      <c r="D124" s="12">
         <f>C124</f>
         <v/>
       </c>
-      <c r="E124" s="7" t="inlineStr">
+      <c r="E124" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="7" t="inlineStr">
+      <c r="A125" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B125" s="7" t="inlineStr">
+      <c r="B125" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C125" s="8">
+      <c r="C125" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FY-9")</f>
         <v/>
       </c>
-      <c r="D125" s="9">
+      <c r="D125" s="12">
         <f>C125</f>
         <v/>
       </c>
-      <c r="E125" s="7" t="inlineStr">
+      <c r="E125" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="7" t="inlineStr">
+      <c r="A126" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B126" s="7" t="inlineStr">
+      <c r="B126" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C126" s="8">
+      <c r="C126" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FY-10")</f>
         <v/>
       </c>
-      <c r="D126" s="9">
+      <c r="D126" s="12">
         <f>C126</f>
         <v/>
       </c>
-      <c r="E126" s="7" t="inlineStr">
+      <c r="E126" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="7" t="inlineStr">
+      <c r="A127" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B127" s="7" t="inlineStr">
+      <c r="B127" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C127" s="8">
+      <c r="C127" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FY-0")</f>
         <v/>
       </c>
-      <c r="D127" s="9">
+      <c r="D127" s="12">
         <f>C127</f>
         <v/>
       </c>
-      <c r="E127" s="7" t="inlineStr">
+      <c r="E127" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="7" t="inlineStr">
+      <c r="A128" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B128" s="7" t="inlineStr">
+      <c r="B128" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C128" s="8">
+      <c r="C128" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FY-1")</f>
         <v/>
       </c>
-      <c r="D128" s="9">
+      <c r="D128" s="12">
         <f>C128</f>
         <v/>
       </c>
-      <c r="E128" s="7" t="inlineStr">
+      <c r="E128" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="7" t="inlineStr">
+      <c r="A129" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B129" s="7" t="inlineStr">
+      <c r="B129" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C129" s="8">
+      <c r="C129" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FY-2")</f>
         <v/>
       </c>
-      <c r="D129" s="9">
+      <c r="D129" s="12">
         <f>C129</f>
         <v/>
       </c>
-      <c r="E129" s="7" t="inlineStr">
+      <c r="E129" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="7" t="inlineStr">
+      <c r="A130" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B130" s="7" t="inlineStr">
+      <c r="B130" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C130" s="8">
+      <c r="C130" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FY-3")</f>
         <v/>
       </c>
-      <c r="D130" s="9">
+      <c r="D130" s="12">
         <f>C130</f>
         <v/>
       </c>
-      <c r="E130" s="7" t="inlineStr">
+      <c r="E130" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="7" t="inlineStr">
+      <c r="A131" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B131" s="7" t="inlineStr">
+      <c r="B131" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C131" s="8">
+      <c r="C131" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FY-4")</f>
         <v/>
       </c>
-      <c r="D131" s="9">
+      <c r="D131" s="12">
         <f>C131</f>
         <v/>
       </c>
-      <c r="E131" s="7" t="inlineStr">
+      <c r="E131" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="7" t="inlineStr">
+      <c r="A132" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B132" s="7" t="inlineStr">
+      <c r="B132" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C132" s="8">
+      <c r="C132" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FY-5")</f>
         <v/>
       </c>
-      <c r="D132" s="9">
+      <c r="D132" s="12">
         <f>C132</f>
         <v/>
       </c>
-      <c r="E132" s="7" t="inlineStr">
+      <c r="E132" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="7" t="inlineStr">
+      <c r="A133" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B133" s="7" t="inlineStr">
+      <c r="B133" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C133" s="8">
+      <c r="C133" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FY-6")</f>
         <v/>
       </c>
-      <c r="D133" s="9">
+      <c r="D133" s="12">
         <f>C133</f>
         <v/>
       </c>
-      <c r="E133" s="7" t="inlineStr">
+      <c r="E133" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="7" t="inlineStr">
+      <c r="A134" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B134" s="7" t="inlineStr">
+      <c r="B134" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C134" s="8">
+      <c r="C134" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FY-7")</f>
         <v/>
       </c>
-      <c r="D134" s="9">
+      <c r="D134" s="12">
         <f>C134</f>
         <v/>
       </c>
-      <c r="E134" s="7" t="inlineStr">
+      <c r="E134" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="7" t="inlineStr">
+      <c r="A135" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B135" s="7" t="inlineStr">
+      <c r="B135" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C135" s="8">
+      <c r="C135" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FY-8")</f>
         <v/>
       </c>
-      <c r="D135" s="9">
+      <c r="D135" s="12">
         <f>C135</f>
         <v/>
       </c>
-      <c r="E135" s="7" t="inlineStr">
+      <c r="E135" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="7" t="inlineStr">
+      <c r="A136" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B136" s="7" t="inlineStr">
+      <c r="B136" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C136" s="8">
+      <c r="C136" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FY-9")</f>
         <v/>
       </c>
-      <c r="D136" s="9">
+      <c r="D136" s="12">
         <f>C136</f>
         <v/>
       </c>
-      <c r="E136" s="7" t="inlineStr">
+      <c r="E136" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="7" t="inlineStr">
+      <c r="A137" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B137" s="7" t="inlineStr">
+      <c r="B137" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C137" s="8">
+      <c r="C137" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FY-10")</f>
         <v/>
       </c>
-      <c r="D137" s="9">
+      <c r="D137" s="12">
         <f>C137</f>
         <v/>
       </c>
-      <c r="E137" s="7" t="inlineStr">
+      <c r="E137" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="6" t="inlineStr">
+      <c r="A138" s="9" t="inlineStr">
         <is>
           <t>INCOME STATEMENT (Quarterly — for LTM)</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="7" t="inlineStr">
+      <c r="A139" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B139" s="7" t="inlineStr">
+      <c r="B139" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C139" s="8">
+      <c r="C139" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FQ-0")</f>
         <v/>
       </c>
-      <c r="D139" s="9">
+      <c r="D139" s="12">
         <f>C139</f>
         <v/>
       </c>
-      <c r="E139" s="7" t="inlineStr">
+      <c r="E139" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="7" t="inlineStr">
+      <c r="A140" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B140" s="7" t="inlineStr">
+      <c r="B140" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-1</t>
         </is>
       </c>
-      <c r="C140" s="8">
+      <c r="C140" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FQ-1")</f>
         <v/>
       </c>
-      <c r="D140" s="9">
+      <c r="D140" s="12">
         <f>C140</f>
         <v/>
       </c>
-      <c r="E140" s="7" t="inlineStr">
+      <c r="E140" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="7" t="inlineStr">
+      <c r="A141" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B141" s="7" t="inlineStr">
+      <c r="B141" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-2</t>
         </is>
       </c>
-      <c r="C141" s="8">
+      <c r="C141" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FQ-2")</f>
         <v/>
       </c>
-      <c r="D141" s="9">
+      <c r="D141" s="12">
         <f>C141</f>
         <v/>
       </c>
-      <c r="E141" s="7" t="inlineStr">
+      <c r="E141" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="7" t="inlineStr">
+      <c r="A142" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B142" s="7" t="inlineStr">
+      <c r="B142" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-3</t>
         </is>
       </c>
-      <c r="C142" s="8">
+      <c r="C142" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FQ-3")</f>
         <v/>
       </c>
-      <c r="D142" s="9">
+      <c r="D142" s="12">
         <f>C142</f>
         <v/>
       </c>
-      <c r="E142" s="7" t="inlineStr">
+      <c r="E142" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="7" t="inlineStr">
+      <c r="A143" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B143" s="7" t="inlineStr">
+      <c r="B143" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-4</t>
         </is>
       </c>
-      <c r="C143" s="8">
+      <c r="C143" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FQ-4")</f>
         <v/>
       </c>
-      <c r="D143" s="9">
+      <c r="D143" s="12">
         <f>C143</f>
         <v/>
       </c>
-      <c r="E143" s="7" t="inlineStr">
+      <c r="E143" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="7" t="inlineStr">
+      <c r="A144" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B144" s="7" t="inlineStr">
+      <c r="B144" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-5</t>
         </is>
       </c>
-      <c r="C144" s="8">
+      <c r="C144" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FQ-5")</f>
         <v/>
       </c>
-      <c r="D144" s="9">
+      <c r="D144" s="12">
         <f>C144</f>
         <v/>
       </c>
-      <c r="E144" s="7" t="inlineStr">
+      <c r="E144" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="7" t="inlineStr">
+      <c r="A145" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B145" s="7" t="inlineStr">
+      <c r="B145" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-6</t>
         </is>
       </c>
-      <c r="C145" s="8">
+      <c r="C145" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FQ-6")</f>
         <v/>
       </c>
-      <c r="D145" s="9">
+      <c r="D145" s="12">
         <f>C145</f>
         <v/>
       </c>
-      <c r="E145" s="7" t="inlineStr">
+      <c r="E145" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="7" t="inlineStr">
+      <c r="A146" s="10" t="inlineStr">
         <is>
           <t>revenues</t>
         </is>
       </c>
-      <c r="B146" s="7" t="inlineStr">
+      <c r="B146" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-7</t>
         </is>
       </c>
-      <c r="C146" s="8">
+      <c r="C146" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_REV","IQ_FQ-7")</f>
         <v/>
       </c>
-      <c r="D146" s="9">
+      <c r="D146" s="12">
         <f>C146</f>
         <v/>
       </c>
-      <c r="E146" s="7" t="inlineStr">
+      <c r="E146" s="10" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="7" t="inlineStr">
+      <c r="A147" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B147" s="7" t="inlineStr">
+      <c r="B147" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C147" s="8">
+      <c r="C147" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FQ-0")</f>
         <v/>
       </c>
-      <c r="D147" s="9">
+      <c r="D147" s="12">
         <f>C147</f>
         <v/>
       </c>
-      <c r="E147" s="7" t="inlineStr">
+      <c r="E147" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="7" t="inlineStr">
+      <c r="A148" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B148" s="7" t="inlineStr">
+      <c r="B148" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-1</t>
         </is>
       </c>
-      <c r="C148" s="8">
+      <c r="C148" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FQ-1")</f>
         <v/>
       </c>
-      <c r="D148" s="9">
+      <c r="D148" s="12">
         <f>C148</f>
         <v/>
       </c>
-      <c r="E148" s="7" t="inlineStr">
+      <c r="E148" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="7" t="inlineStr">
+      <c r="A149" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B149" s="7" t="inlineStr">
+      <c r="B149" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-2</t>
         </is>
       </c>
-      <c r="C149" s="8">
+      <c r="C149" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FQ-2")</f>
         <v/>
       </c>
-      <c r="D149" s="9">
+      <c r="D149" s="12">
         <f>C149</f>
         <v/>
       </c>
-      <c r="E149" s="7" t="inlineStr">
+      <c r="E149" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="7" t="inlineStr">
+      <c r="A150" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B150" s="7" t="inlineStr">
+      <c r="B150" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-3</t>
         </is>
       </c>
-      <c r="C150" s="8">
+      <c r="C150" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FQ-3")</f>
         <v/>
       </c>
-      <c r="D150" s="9">
+      <c r="D150" s="12">
         <f>C150</f>
         <v/>
       </c>
-      <c r="E150" s="7" t="inlineStr">
+      <c r="E150" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="7" t="inlineStr">
+      <c r="A151" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B151" s="7" t="inlineStr">
+      <c r="B151" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-4</t>
         </is>
       </c>
-      <c r="C151" s="8">
+      <c r="C151" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FQ-4")</f>
         <v/>
       </c>
-      <c r="D151" s="9">
+      <c r="D151" s="12">
         <f>C151</f>
         <v/>
       </c>
-      <c r="E151" s="7" t="inlineStr">
+      <c r="E151" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="7" t="inlineStr">
+      <c r="A152" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B152" s="7" t="inlineStr">
+      <c r="B152" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-5</t>
         </is>
       </c>
-      <c r="C152" s="8">
+      <c r="C152" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FQ-5")</f>
         <v/>
       </c>
-      <c r="D152" s="9">
+      <c r="D152" s="12">
         <f>C152</f>
         <v/>
       </c>
-      <c r="E152" s="7" t="inlineStr">
+      <c r="E152" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="7" t="inlineStr">
+      <c r="A153" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B153" s="7" t="inlineStr">
+      <c r="B153" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-6</t>
         </is>
       </c>
-      <c r="C153" s="8">
+      <c r="C153" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FQ-6")</f>
         <v/>
       </c>
-      <c r="D153" s="9">
+      <c r="D153" s="12">
         <f>C153</f>
         <v/>
       </c>
-      <c r="E153" s="7" t="inlineStr">
+      <c r="E153" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="7" t="inlineStr">
+      <c r="A154" s="10" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="B154" s="7" t="inlineStr">
+      <c r="B154" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-7</t>
         </is>
       </c>
-      <c r="C154" s="8">
+      <c r="C154" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBIT","IQ_FQ-7")</f>
         <v/>
       </c>
-      <c r="D154" s="9">
+      <c r="D154" s="12">
         <f>C154</f>
         <v/>
       </c>
-      <c r="E154" s="7" t="inlineStr">
+      <c r="E154" s="10" t="inlineStr">
         <is>
           <t>Operating Income (EBIT)</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="7" t="inlineStr">
+      <c r="A155" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B155" s="7" t="inlineStr">
+      <c r="B155" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C155" s="8">
+      <c r="C155" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FQ-0")</f>
         <v/>
       </c>
-      <c r="D155" s="9">
+      <c r="D155" s="12">
         <f>C155</f>
         <v/>
       </c>
-      <c r="E155" s="7" t="inlineStr">
+      <c r="E155" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="7" t="inlineStr">
+      <c r="A156" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B156" s="7" t="inlineStr">
+      <c r="B156" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-1</t>
         </is>
       </c>
-      <c r="C156" s="8">
+      <c r="C156" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FQ-1")</f>
         <v/>
       </c>
-      <c r="D156" s="9">
+      <c r="D156" s="12">
         <f>C156</f>
         <v/>
       </c>
-      <c r="E156" s="7" t="inlineStr">
+      <c r="E156" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="7" t="inlineStr">
+      <c r="A157" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B157" s="7" t="inlineStr">
+      <c r="B157" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-2</t>
         </is>
       </c>
-      <c r="C157" s="8">
+      <c r="C157" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FQ-2")</f>
         <v/>
       </c>
-      <c r="D157" s="9">
+      <c r="D157" s="12">
         <f>C157</f>
         <v/>
       </c>
-      <c r="E157" s="7" t="inlineStr">
+      <c r="E157" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="7" t="inlineStr">
+      <c r="A158" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B158" s="7" t="inlineStr">
+      <c r="B158" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-3</t>
         </is>
       </c>
-      <c r="C158" s="8">
+      <c r="C158" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FQ-3")</f>
         <v/>
       </c>
-      <c r="D158" s="9">
+      <c r="D158" s="12">
         <f>C158</f>
         <v/>
       </c>
-      <c r="E158" s="7" t="inlineStr">
+      <c r="E158" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="7" t="inlineStr">
+      <c r="A159" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B159" s="7" t="inlineStr">
+      <c r="B159" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-4</t>
         </is>
       </c>
-      <c r="C159" s="8">
+      <c r="C159" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FQ-4")</f>
         <v/>
       </c>
-      <c r="D159" s="9">
+      <c r="D159" s="12">
         <f>C159</f>
         <v/>
       </c>
-      <c r="E159" s="7" t="inlineStr">
+      <c r="E159" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="7" t="inlineStr">
+      <c r="A160" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B160" s="7" t="inlineStr">
+      <c r="B160" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-5</t>
         </is>
       </c>
-      <c r="C160" s="8">
+      <c r="C160" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FQ-5")</f>
         <v/>
       </c>
-      <c r="D160" s="9">
+      <c r="D160" s="12">
         <f>C160</f>
         <v/>
       </c>
-      <c r="E160" s="7" t="inlineStr">
+      <c r="E160" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="7" t="inlineStr">
+      <c r="A161" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B161" s="7" t="inlineStr">
+      <c r="B161" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-6</t>
         </is>
       </c>
-      <c r="C161" s="8">
+      <c r="C161" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FQ-6")</f>
         <v/>
       </c>
-      <c r="D161" s="9">
+      <c r="D161" s="12">
         <f>C161</f>
         <v/>
       </c>
-      <c r="E161" s="7" t="inlineStr">
+      <c r="E161" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="7" t="inlineStr">
+      <c r="A162" s="10" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B162" s="7" t="inlineStr">
+      <c r="B162" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-7</t>
         </is>
       </c>
-      <c r="C162" s="8">
+      <c r="C162" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBITDA","IQ_FQ-7")</f>
         <v/>
       </c>
-      <c r="D162" s="9">
+      <c r="D162" s="12">
         <f>C162</f>
         <v/>
       </c>
-      <c r="E162" s="7" t="inlineStr">
+      <c r="E162" s="10" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="7" t="inlineStr">
+      <c r="A163" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B163" s="7" t="inlineStr">
+      <c r="B163" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C163" s="8">
+      <c r="C163" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FQ-0")</f>
         <v/>
       </c>
-      <c r="D163" s="9">
+      <c r="D163" s="12">
         <f>C163</f>
         <v/>
       </c>
-      <c r="E163" s="7" t="inlineStr">
+      <c r="E163" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="7" t="inlineStr">
+      <c r="A164" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B164" s="7" t="inlineStr">
+      <c r="B164" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-1</t>
         </is>
       </c>
-      <c r="C164" s="8">
+      <c r="C164" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FQ-1")</f>
         <v/>
       </c>
-      <c r="D164" s="9">
+      <c r="D164" s="12">
         <f>C164</f>
         <v/>
       </c>
-      <c r="E164" s="7" t="inlineStr">
+      <c r="E164" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="7" t="inlineStr">
+      <c r="A165" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B165" s="7" t="inlineStr">
+      <c r="B165" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-2</t>
         </is>
       </c>
-      <c r="C165" s="8">
+      <c r="C165" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FQ-2")</f>
         <v/>
       </c>
-      <c r="D165" s="9">
+      <c r="D165" s="12">
         <f>C165</f>
         <v/>
       </c>
-      <c r="E165" s="7" t="inlineStr">
+      <c r="E165" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="7" t="inlineStr">
+      <c r="A166" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B166" s="7" t="inlineStr">
+      <c r="B166" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-3</t>
         </is>
       </c>
-      <c r="C166" s="8">
+      <c r="C166" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FQ-3")</f>
         <v/>
       </c>
-      <c r="D166" s="9">
+      <c r="D166" s="12">
         <f>C166</f>
         <v/>
       </c>
-      <c r="E166" s="7" t="inlineStr">
+      <c r="E166" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="7" t="inlineStr">
+      <c r="A167" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B167" s="7" t="inlineStr">
+      <c r="B167" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-4</t>
         </is>
       </c>
-      <c r="C167" s="8">
+      <c r="C167" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FQ-4")</f>
         <v/>
       </c>
-      <c r="D167" s="9">
+      <c r="D167" s="12">
         <f>C167</f>
         <v/>
       </c>
-      <c r="E167" s="7" t="inlineStr">
+      <c r="E167" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="7" t="inlineStr">
+      <c r="A168" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B168" s="7" t="inlineStr">
+      <c r="B168" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-5</t>
         </is>
       </c>
-      <c r="C168" s="8">
+      <c r="C168" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FQ-5")</f>
         <v/>
       </c>
-      <c r="D168" s="9">
+      <c r="D168" s="12">
         <f>C168</f>
         <v/>
       </c>
-      <c r="E168" s="7" t="inlineStr">
+      <c r="E168" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="7" t="inlineStr">
+      <c r="A169" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B169" s="7" t="inlineStr">
+      <c r="B169" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-6</t>
         </is>
       </c>
-      <c r="C169" s="8">
+      <c r="C169" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FQ-6")</f>
         <v/>
       </c>
-      <c r="D169" s="9">
+      <c r="D169" s="12">
         <f>C169</f>
         <v/>
       </c>
-      <c r="E169" s="7" t="inlineStr">
+      <c r="E169" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="7" t="inlineStr">
+      <c r="A170" s="10" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="B170" s="7" t="inlineStr">
+      <c r="B170" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-7</t>
         </is>
       </c>
-      <c r="C170" s="8">
+      <c r="C170" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_NI","IQ_FQ-7")</f>
         <v/>
       </c>
-      <c r="D170" s="9">
+      <c r="D170" s="12">
         <f>C170</f>
         <v/>
       </c>
-      <c r="E170" s="7" t="inlineStr">
+      <c r="E170" s="10" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="7" t="inlineStr">
+      <c r="A171" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B171" s="7" t="inlineStr">
+      <c r="B171" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C171" s="8">
+      <c r="C171" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FQ-0"))</f>
         <v/>
       </c>
-      <c r="D171" s="9">
+      <c r="D171" s="12">
         <f>C171</f>
         <v/>
       </c>
-      <c r="E171" s="7" t="inlineStr">
+      <c r="E171" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="7" t="inlineStr">
+      <c r="A172" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B172" s="7" t="inlineStr">
+      <c r="B172" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-1</t>
         </is>
       </c>
-      <c r="C172" s="8">
+      <c r="C172" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FQ-1"))</f>
         <v/>
       </c>
-      <c r="D172" s="9">
+      <c r="D172" s="12">
         <f>C172</f>
         <v/>
       </c>
-      <c r="E172" s="7" t="inlineStr">
+      <c r="E172" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="7" t="inlineStr">
+      <c r="A173" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B173" s="7" t="inlineStr">
+      <c r="B173" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-2</t>
         </is>
       </c>
-      <c r="C173" s="8">
+      <c r="C173" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FQ-2"))</f>
         <v/>
       </c>
-      <c r="D173" s="9">
+      <c r="D173" s="12">
         <f>C173</f>
         <v/>
       </c>
-      <c r="E173" s="7" t="inlineStr">
+      <c r="E173" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="7" t="inlineStr">
+      <c r="A174" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B174" s="7" t="inlineStr">
+      <c r="B174" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-3</t>
         </is>
       </c>
-      <c r="C174" s="8">
+      <c r="C174" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FQ-3"))</f>
         <v/>
       </c>
-      <c r="D174" s="9">
+      <c r="D174" s="12">
         <f>C174</f>
         <v/>
       </c>
-      <c r="E174" s="7" t="inlineStr">
+      <c r="E174" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="7" t="inlineStr">
+      <c r="A175" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B175" s="7" t="inlineStr">
+      <c r="B175" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-4</t>
         </is>
       </c>
-      <c r="C175" s="8">
+      <c r="C175" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FQ-4"))</f>
         <v/>
       </c>
-      <c r="D175" s="9">
+      <c r="D175" s="12">
         <f>C175</f>
         <v/>
       </c>
-      <c r="E175" s="7" t="inlineStr">
+      <c r="E175" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="7" t="inlineStr">
+      <c r="A176" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B176" s="7" t="inlineStr">
+      <c r="B176" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-5</t>
         </is>
       </c>
-      <c r="C176" s="8">
+      <c r="C176" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FQ-5"))</f>
         <v/>
       </c>
-      <c r="D176" s="9">
+      <c r="D176" s="12">
         <f>C176</f>
         <v/>
       </c>
-      <c r="E176" s="7" t="inlineStr">
+      <c r="E176" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="7" t="inlineStr">
+      <c r="A177" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B177" s="7" t="inlineStr">
+      <c r="B177" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-6</t>
         </is>
       </c>
-      <c r="C177" s="8">
+      <c r="C177" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FQ-6"))</f>
         <v/>
       </c>
-      <c r="D177" s="9">
+      <c r="D177" s="12">
         <f>C177</f>
         <v/>
       </c>
-      <c r="E177" s="7" t="inlineStr">
+      <c r="E177" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="7" t="inlineStr">
+      <c r="A178" s="10" t="inlineStr">
         <is>
           <t>interest_expense</t>
         </is>
       </c>
-      <c r="B178" s="7" t="inlineStr">
+      <c r="B178" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-7</t>
         </is>
       </c>
-      <c r="C178" s="8">
+      <c r="C178" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INTEREST_EXP","IQ_FQ-7"))</f>
         <v/>
       </c>
-      <c r="D178" s="9">
+      <c r="D178" s="12">
         <f>C178</f>
         <v/>
       </c>
-      <c r="E178" s="7" t="inlineStr">
+      <c r="E178" s="10" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="7" t="inlineStr">
+      <c r="A179" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B179" s="7" t="inlineStr">
+      <c r="B179" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C179" s="8">
+      <c r="C179" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FQ-0"))</f>
         <v/>
       </c>
-      <c r="D179" s="9">
+      <c r="D179" s="12">
         <f>C179</f>
         <v/>
       </c>
-      <c r="E179" s="7" t="inlineStr">
+      <c r="E179" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="7" t="inlineStr">
+      <c r="A180" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B180" s="7" t="inlineStr">
+      <c r="B180" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-1</t>
         </is>
       </c>
-      <c r="C180" s="8">
+      <c r="C180" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FQ-1"))</f>
         <v/>
       </c>
-      <c r="D180" s="9">
+      <c r="D180" s="12">
         <f>C180</f>
         <v/>
       </c>
-      <c r="E180" s="7" t="inlineStr">
+      <c r="E180" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="7" t="inlineStr">
+      <c r="A181" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B181" s="7" t="inlineStr">
+      <c r="B181" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-2</t>
         </is>
       </c>
-      <c r="C181" s="8">
+      <c r="C181" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FQ-2"))</f>
         <v/>
       </c>
-      <c r="D181" s="9">
+      <c r="D181" s="12">
         <f>C181</f>
         <v/>
       </c>
-      <c r="E181" s="7" t="inlineStr">
+      <c r="E181" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="7" t="inlineStr">
+      <c r="A182" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B182" s="7" t="inlineStr">
+      <c r="B182" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-3</t>
         </is>
       </c>
-      <c r="C182" s="8">
+      <c r="C182" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FQ-3"))</f>
         <v/>
       </c>
-      <c r="D182" s="9">
+      <c r="D182" s="12">
         <f>C182</f>
         <v/>
       </c>
-      <c r="E182" s="7" t="inlineStr">
+      <c r="E182" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="7" t="inlineStr">
+      <c r="A183" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B183" s="7" t="inlineStr">
+      <c r="B183" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-4</t>
         </is>
       </c>
-      <c r="C183" s="8">
+      <c r="C183" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FQ-4"))</f>
         <v/>
       </c>
-      <c r="D183" s="9">
+      <c r="D183" s="12">
         <f>C183</f>
         <v/>
       </c>
-      <c r="E183" s="7" t="inlineStr">
+      <c r="E183" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="7" t="inlineStr">
+      <c r="A184" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B184" s="7" t="inlineStr">
+      <c r="B184" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-5</t>
         </is>
       </c>
-      <c r="C184" s="8">
+      <c r="C184" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FQ-5"))</f>
         <v/>
       </c>
-      <c r="D184" s="9">
+      <c r="D184" s="12">
         <f>C184</f>
         <v/>
       </c>
-      <c r="E184" s="7" t="inlineStr">
+      <c r="E184" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="7" t="inlineStr">
+      <c r="A185" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B185" s="7" t="inlineStr">
+      <c r="B185" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-6</t>
         </is>
       </c>
-      <c r="C185" s="8">
+      <c r="C185" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FQ-6"))</f>
         <v/>
       </c>
-      <c r="D185" s="9">
+      <c r="D185" s="12">
         <f>C185</f>
         <v/>
       </c>
-      <c r="E185" s="7" t="inlineStr">
+      <c r="E185" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="7" t="inlineStr">
+      <c r="A186" s="10" t="inlineStr">
         <is>
           <t>d_a</t>
         </is>
       </c>
-      <c r="B186" s="7" t="inlineStr">
+      <c r="B186" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-7</t>
         </is>
       </c>
-      <c r="C186" s="8">
+      <c r="C186" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_DA_CF","IQ_FQ-7"))</f>
         <v/>
       </c>
-      <c r="D186" s="9">
+      <c r="D186" s="12">
         <f>C186</f>
         <v/>
       </c>
-      <c r="E186" s="7" t="inlineStr">
+      <c r="E186" s="10" t="inlineStr">
         <is>
           <t>Depreciation &amp; Amortization (from Cash Flow)</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="7" t="inlineStr">
+      <c r="A187" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B187" s="7" t="inlineStr">
+      <c r="B187" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C187" s="8">
+      <c r="C187" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FQ-0")</f>
         <v/>
       </c>
-      <c r="D187" s="9">
+      <c r="D187" s="12">
         <f>C187</f>
         <v/>
       </c>
-      <c r="E187" s="7" t="inlineStr">
+      <c r="E187" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="7" t="inlineStr">
+      <c r="A188" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B188" s="7" t="inlineStr">
+      <c r="B188" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-1</t>
         </is>
       </c>
-      <c r="C188" s="8">
+      <c r="C188" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FQ-1")</f>
         <v/>
       </c>
-      <c r="D188" s="9">
+      <c r="D188" s="12">
         <f>C188</f>
         <v/>
       </c>
-      <c r="E188" s="7" t="inlineStr">
+      <c r="E188" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="7" t="inlineStr">
+      <c r="A189" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B189" s="7" t="inlineStr">
+      <c r="B189" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-2</t>
         </is>
       </c>
-      <c r="C189" s="8">
+      <c r="C189" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FQ-2")</f>
         <v/>
       </c>
-      <c r="D189" s="9">
+      <c r="D189" s="12">
         <f>C189</f>
         <v/>
       </c>
-      <c r="E189" s="7" t="inlineStr">
+      <c r="E189" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="7" t="inlineStr">
+      <c r="A190" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B190" s="7" t="inlineStr">
+      <c r="B190" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-3</t>
         </is>
       </c>
-      <c r="C190" s="8">
+      <c r="C190" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FQ-3")</f>
         <v/>
       </c>
-      <c r="D190" s="9">
+      <c r="D190" s="12">
         <f>C190</f>
         <v/>
       </c>
-      <c r="E190" s="7" t="inlineStr">
+      <c r="E190" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="7" t="inlineStr">
+      <c r="A191" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B191" s="7" t="inlineStr">
+      <c r="B191" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-4</t>
         </is>
       </c>
-      <c r="C191" s="8">
+      <c r="C191" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FQ-4")</f>
         <v/>
       </c>
-      <c r="D191" s="9">
+      <c r="D191" s="12">
         <f>C191</f>
         <v/>
       </c>
-      <c r="E191" s="7" t="inlineStr">
+      <c r="E191" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="7" t="inlineStr">
+      <c r="A192" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B192" s="7" t="inlineStr">
+      <c r="B192" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-5</t>
         </is>
       </c>
-      <c r="C192" s="8">
+      <c r="C192" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FQ-5")</f>
         <v/>
       </c>
-      <c r="D192" s="9">
+      <c r="D192" s="12">
         <f>C192</f>
         <v/>
       </c>
-      <c r="E192" s="7" t="inlineStr">
+      <c r="E192" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="7" t="inlineStr">
+      <c r="A193" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B193" s="7" t="inlineStr">
+      <c r="B193" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-6</t>
         </is>
       </c>
-      <c r="C193" s="8">
+      <c r="C193" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FQ-6")</f>
         <v/>
       </c>
-      <c r="D193" s="9">
+      <c r="D193" s="12">
         <f>C193</f>
         <v/>
       </c>
-      <c r="E193" s="7" t="inlineStr">
+      <c r="E193" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="7" t="inlineStr">
+      <c r="A194" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense</t>
         </is>
       </c>
-      <c r="B194" s="7" t="inlineStr">
+      <c r="B194" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-7</t>
         </is>
       </c>
-      <c r="C194" s="8">
+      <c r="C194" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP","IQ_FQ-7")</f>
         <v/>
       </c>
-      <c r="D194" s="9">
+      <c r="D194" s="12">
         <f>C194</f>
         <v/>
       </c>
-      <c r="E194" s="7" t="inlineStr">
+      <c r="E194" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="7" t="inlineStr">
+      <c r="A195" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B195" s="7" t="inlineStr">
+      <c r="B195" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C195" s="8">
+      <c r="C195" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FQ-0")</f>
         <v/>
       </c>
-      <c r="D195" s="9">
+      <c r="D195" s="12">
         <f>C195</f>
         <v/>
       </c>
-      <c r="E195" s="7" t="inlineStr">
+      <c r="E195" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="7" t="inlineStr">
+      <c r="A196" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B196" s="7" t="inlineStr">
+      <c r="B196" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-1</t>
         </is>
       </c>
-      <c r="C196" s="8">
+      <c r="C196" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FQ-1")</f>
         <v/>
       </c>
-      <c r="D196" s="9">
+      <c r="D196" s="12">
         <f>C196</f>
         <v/>
       </c>
-      <c r="E196" s="7" t="inlineStr">
+      <c r="E196" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="7" t="inlineStr">
+      <c r="A197" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B197" s="7" t="inlineStr">
+      <c r="B197" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-2</t>
         </is>
       </c>
-      <c r="C197" s="8">
+      <c r="C197" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FQ-2")</f>
         <v/>
       </c>
-      <c r="D197" s="9">
+      <c r="D197" s="12">
         <f>C197</f>
         <v/>
       </c>
-      <c r="E197" s="7" t="inlineStr">
+      <c r="E197" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="7" t="inlineStr">
+      <c r="A198" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B198" s="7" t="inlineStr">
+      <c r="B198" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-3</t>
         </is>
       </c>
-      <c r="C198" s="8">
+      <c r="C198" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FQ-3")</f>
         <v/>
       </c>
-      <c r="D198" s="9">
+      <c r="D198" s="12">
         <f>C198</f>
         <v/>
       </c>
-      <c r="E198" s="7" t="inlineStr">
+      <c r="E198" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="7" t="inlineStr">
+      <c r="A199" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B199" s="7" t="inlineStr">
+      <c r="B199" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-4</t>
         </is>
       </c>
-      <c r="C199" s="8">
+      <c r="C199" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FQ-4")</f>
         <v/>
       </c>
-      <c r="D199" s="9">
+      <c r="D199" s="12">
         <f>C199</f>
         <v/>
       </c>
-      <c r="E199" s="7" t="inlineStr">
+      <c r="E199" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="7" t="inlineStr">
+      <c r="A200" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B200" s="7" t="inlineStr">
+      <c r="B200" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-5</t>
         </is>
       </c>
-      <c r="C200" s="8">
+      <c r="C200" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FQ-5")</f>
         <v/>
       </c>
-      <c r="D200" s="9">
+      <c r="D200" s="12">
         <f>C200</f>
         <v/>
       </c>
-      <c r="E200" s="7" t="inlineStr">
+      <c r="E200" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="7" t="inlineStr">
+      <c r="A201" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B201" s="7" t="inlineStr">
+      <c r="B201" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-6</t>
         </is>
       </c>
-      <c r="C201" s="8">
+      <c r="C201" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FQ-6")</f>
         <v/>
       </c>
-      <c r="D201" s="9">
+      <c r="D201" s="12">
         <f>C201</f>
         <v/>
       </c>
-      <c r="E201" s="7" t="inlineStr">
+      <c r="E201" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="7" t="inlineStr">
+      <c r="A202" s="10" t="inlineStr">
         <is>
           <t>r_and_d_expense_fn</t>
         </is>
       </c>
-      <c r="B202" s="7" t="inlineStr">
+      <c r="B202" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-7</t>
         </is>
       </c>
-      <c r="C202" s="8">
+      <c r="C202" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_RD_EXP_FN","IQ_FQ-7")</f>
         <v/>
       </c>
-      <c r="D202" s="9">
+      <c r="D202" s="12">
         <f>C202</f>
         <v/>
       </c>
-      <c r="E202" s="7" t="inlineStr">
+      <c r="E202" s="10" t="inlineStr">
         <is>
           <t>R&amp;D Expense (footnote fallback)</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="7" t="inlineStr">
+      <c r="A203" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B203" s="7" t="inlineStr">
+      <c r="B203" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C203" s="8">
+      <c r="C203" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FQ-0"))</f>
         <v/>
       </c>
-      <c r="D203" s="9">
+      <c r="D203" s="12">
         <f>C203</f>
         <v/>
       </c>
-      <c r="E203" s="7" t="inlineStr">
+      <c r="E203" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="7" t="inlineStr">
+      <c r="A204" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B204" s="7" t="inlineStr">
+      <c r="B204" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-1</t>
         </is>
       </c>
-      <c r="C204" s="8">
+      <c r="C204" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FQ-1"))</f>
         <v/>
       </c>
-      <c r="D204" s="9">
+      <c r="D204" s="12">
         <f>C204</f>
         <v/>
       </c>
-      <c r="E204" s="7" t="inlineStr">
+      <c r="E204" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="7" t="inlineStr">
+      <c r="A205" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B205" s="7" t="inlineStr">
+      <c r="B205" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-2</t>
         </is>
       </c>
-      <c r="C205" s="8">
+      <c r="C205" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FQ-2"))</f>
         <v/>
       </c>
-      <c r="D205" s="9">
+      <c r="D205" s="12">
         <f>C205</f>
         <v/>
       </c>
-      <c r="E205" s="7" t="inlineStr">
+      <c r="E205" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="7" t="inlineStr">
+      <c r="A206" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B206" s="7" t="inlineStr">
+      <c r="B206" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-3</t>
         </is>
       </c>
-      <c r="C206" s="8">
+      <c r="C206" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FQ-3"))</f>
         <v/>
       </c>
-      <c r="D206" s="9">
+      <c r="D206" s="12">
         <f>C206</f>
         <v/>
       </c>
-      <c r="E206" s="7" t="inlineStr">
+      <c r="E206" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="7" t="inlineStr">
+      <c r="A207" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B207" s="7" t="inlineStr">
+      <c r="B207" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-4</t>
         </is>
       </c>
-      <c r="C207" s="8">
+      <c r="C207" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FQ-4"))</f>
         <v/>
       </c>
-      <c r="D207" s="9">
+      <c r="D207" s="12">
         <f>C207</f>
         <v/>
       </c>
-      <c r="E207" s="7" t="inlineStr">
+      <c r="E207" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="7" t="inlineStr">
+      <c r="A208" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B208" s="7" t="inlineStr">
+      <c r="B208" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-5</t>
         </is>
       </c>
-      <c r="C208" s="8">
+      <c r="C208" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FQ-5"))</f>
         <v/>
       </c>
-      <c r="D208" s="9">
+      <c r="D208" s="12">
         <f>C208</f>
         <v/>
       </c>
-      <c r="E208" s="7" t="inlineStr">
+      <c r="E208" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="7" t="inlineStr">
+      <c r="A209" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B209" s="7" t="inlineStr">
+      <c r="B209" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-6</t>
         </is>
       </c>
-      <c r="C209" s="8">
+      <c r="C209" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FQ-6"))</f>
         <v/>
       </c>
-      <c r="D209" s="9">
+      <c r="D209" s="12">
         <f>C209</f>
         <v/>
       </c>
-      <c r="E209" s="7" t="inlineStr">
+      <c r="E209" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="7" t="inlineStr">
+      <c r="A210" s="10" t="inlineStr">
         <is>
           <t>capex</t>
         </is>
       </c>
-      <c r="B210" s="7" t="inlineStr">
+      <c r="B210" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-7</t>
         </is>
       </c>
-      <c r="C210" s="8">
+      <c r="C210" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CAPEX","IQ_FQ-7"))</f>
         <v/>
       </c>
-      <c r="D210" s="9">
+      <c r="D210" s="12">
         <f>C210</f>
         <v/>
       </c>
-      <c r="E210" s="7" t="inlineStr">
+      <c r="E210" s="10" t="inlineStr">
         <is>
           <t>Capital Expenditures</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="7" t="inlineStr">
+      <c r="A211" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B211" s="7" t="inlineStr">
+      <c r="B211" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C211" s="8">
+      <c r="C211" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FQ-0"))</f>
         <v/>
       </c>
-      <c r="D211" s="9">
+      <c r="D211" s="12">
         <f>C211</f>
         <v/>
       </c>
-      <c r="E211" s="7" t="inlineStr">
+      <c r="E211" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="7" t="inlineStr">
+      <c r="A212" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B212" s="7" t="inlineStr">
+      <c r="B212" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-1</t>
         </is>
       </c>
-      <c r="C212" s="8">
+      <c r="C212" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FQ-1"))</f>
         <v/>
       </c>
-      <c r="D212" s="9">
+      <c r="D212" s="12">
         <f>C212</f>
         <v/>
       </c>
-      <c r="E212" s="7" t="inlineStr">
+      <c r="E212" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="7" t="inlineStr">
+      <c r="A213" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B213" s="7" t="inlineStr">
+      <c r="B213" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-2</t>
         </is>
       </c>
-      <c r="C213" s="8">
+      <c r="C213" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FQ-2"))</f>
         <v/>
       </c>
-      <c r="D213" s="9">
+      <c r="D213" s="12">
         <f>C213</f>
         <v/>
       </c>
-      <c r="E213" s="7" t="inlineStr">
+      <c r="E213" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="7" t="inlineStr">
+      <c r="A214" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B214" s="7" t="inlineStr">
+      <c r="B214" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-3</t>
         </is>
       </c>
-      <c r="C214" s="8">
+      <c r="C214" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FQ-3"))</f>
         <v/>
       </c>
-      <c r="D214" s="9">
+      <c r="D214" s="12">
         <f>C214</f>
         <v/>
       </c>
-      <c r="E214" s="7" t="inlineStr">
+      <c r="E214" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="7" t="inlineStr">
+      <c r="A215" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B215" s="7" t="inlineStr">
+      <c r="B215" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-4</t>
         </is>
       </c>
-      <c r="C215" s="8">
+      <c r="C215" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FQ-4"))</f>
         <v/>
       </c>
-      <c r="D215" s="9">
+      <c r="D215" s="12">
         <f>C215</f>
         <v/>
       </c>
-      <c r="E215" s="7" t="inlineStr">
+      <c r="E215" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="7" t="inlineStr">
+      <c r="A216" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B216" s="7" t="inlineStr">
+      <c r="B216" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-5</t>
         </is>
       </c>
-      <c r="C216" s="8">
+      <c r="C216" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FQ-5"))</f>
         <v/>
       </c>
-      <c r="D216" s="9">
+      <c r="D216" s="12">
         <f>C216</f>
         <v/>
       </c>
-      <c r="E216" s="7" t="inlineStr">
+      <c r="E216" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="7" t="inlineStr">
+      <c r="A217" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B217" s="7" t="inlineStr">
+      <c r="B217" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-6</t>
         </is>
       </c>
-      <c r="C217" s="8">
+      <c r="C217" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FQ-6"))</f>
         <v/>
       </c>
-      <c r="D217" s="9">
+      <c r="D217" s="12">
         <f>C217</f>
         <v/>
       </c>
-      <c r="E217" s="7" t="inlineStr">
+      <c r="E217" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="7" t="inlineStr">
+      <c r="A218" s="10" t="inlineStr">
         <is>
           <t>operating_lease_expense</t>
         </is>
       </c>
-      <c r="B218" s="7" t="inlineStr">
+      <c r="B218" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-7</t>
         </is>
       </c>
-      <c r="C218" s="8">
+      <c r="C218" s="11">
         <f>ABS(_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPERATING_LEASE_PAYMENTS","IQ_FQ-7"))</f>
         <v/>
       </c>
-      <c r="D218" s="9">
+      <c r="D218" s="12">
         <f>C218</f>
         <v/>
       </c>
-      <c r="E218" s="7" t="inlineStr">
+      <c r="E218" s="10" t="inlineStr">
         <is>
           <t>Operating Lease Payments</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="7" t="inlineStr">
+      <c r="A219" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B219" s="7" t="inlineStr">
+      <c r="B219" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C219" s="8">
+      <c r="C219" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FQ-0")</f>
         <v/>
       </c>
-      <c r="D219" s="9">
+      <c r="D219" s="12">
         <f>C219</f>
         <v/>
       </c>
-      <c r="E219" s="7" t="inlineStr">
+      <c r="E219" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="7" t="inlineStr">
+      <c r="A220" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B220" s="7" t="inlineStr">
+      <c r="B220" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-1</t>
         </is>
       </c>
-      <c r="C220" s="8">
+      <c r="C220" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FQ-1")</f>
         <v/>
       </c>
-      <c r="D220" s="9">
+      <c r="D220" s="12">
         <f>C220</f>
         <v/>
       </c>
-      <c r="E220" s="7" t="inlineStr">
+      <c r="E220" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="7" t="inlineStr">
+      <c r="A221" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B221" s="7" t="inlineStr">
+      <c r="B221" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-2</t>
         </is>
       </c>
-      <c r="C221" s="8">
+      <c r="C221" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FQ-2")</f>
         <v/>
       </c>
-      <c r="D221" s="9">
+      <c r="D221" s="12">
         <f>C221</f>
         <v/>
       </c>
-      <c r="E221" s="7" t="inlineStr">
+      <c r="E221" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="7" t="inlineStr">
+      <c r="A222" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B222" s="7" t="inlineStr">
+      <c r="B222" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-3</t>
         </is>
       </c>
-      <c r="C222" s="8">
+      <c r="C222" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FQ-3")</f>
         <v/>
       </c>
-      <c r="D222" s="9">
+      <c r="D222" s="12">
         <f>C222</f>
         <v/>
       </c>
-      <c r="E222" s="7" t="inlineStr">
+      <c r="E222" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="7" t="inlineStr">
+      <c r="A223" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B223" s="7" t="inlineStr">
+      <c r="B223" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-4</t>
         </is>
       </c>
-      <c r="C223" s="8">
+      <c r="C223" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FQ-4")</f>
         <v/>
       </c>
-      <c r="D223" s="9">
+      <c r="D223" s="12">
         <f>C223</f>
         <v/>
       </c>
-      <c r="E223" s="7" t="inlineStr">
+      <c r="E223" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="7" t="inlineStr">
+      <c r="A224" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B224" s="7" t="inlineStr">
+      <c r="B224" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-5</t>
         </is>
       </c>
-      <c r="C224" s="8">
+      <c r="C224" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FQ-5")</f>
         <v/>
       </c>
-      <c r="D224" s="9">
+      <c r="D224" s="12">
         <f>C224</f>
         <v/>
       </c>
-      <c r="E224" s="7" t="inlineStr">
+      <c r="E224" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="7" t="inlineStr">
+      <c r="A225" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B225" s="7" t="inlineStr">
+      <c r="B225" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-6</t>
         </is>
       </c>
-      <c r="C225" s="8">
+      <c r="C225" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FQ-6")</f>
         <v/>
       </c>
-      <c r="D225" s="9">
+      <c r="D225" s="12">
         <f>C225</f>
         <v/>
       </c>
-      <c r="E225" s="7" t="inlineStr">
+      <c r="E225" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="7" t="inlineStr">
+      <c r="A226" s="10" t="inlineStr">
         <is>
           <t>earnings_before_tax</t>
         </is>
       </c>
-      <c r="B226" s="7" t="inlineStr">
+      <c r="B226" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-7</t>
         </is>
       </c>
-      <c r="C226" s="8">
+      <c r="C226" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EBT_EXCL","IQ_FQ-7")</f>
         <v/>
       </c>
-      <c r="D226" s="9">
+      <c r="D226" s="12">
         <f>C226</f>
         <v/>
       </c>
-      <c r="E226" s="7" t="inlineStr">
+      <c r="E226" s="10" t="inlineStr">
         <is>
           <t>Earnings Before Tax (excl unusual items)</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="7" t="inlineStr">
+      <c r="A227" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B227" s="7" t="inlineStr">
+      <c r="B227" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C227" s="8">
+      <c r="C227" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FQ-0")</f>
         <v/>
       </c>
-      <c r="D227" s="9">
+      <c r="D227" s="12">
         <f>C227</f>
         <v/>
       </c>
-      <c r="E227" s="7" t="inlineStr">
+      <c r="E227" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="7" t="inlineStr">
+      <c r="A228" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B228" s="7" t="inlineStr">
+      <c r="B228" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-1</t>
         </is>
       </c>
-      <c r="C228" s="8">
+      <c r="C228" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FQ-1")</f>
         <v/>
       </c>
-      <c r="D228" s="9">
+      <c r="D228" s="12">
         <f>C228</f>
         <v/>
       </c>
-      <c r="E228" s="7" t="inlineStr">
+      <c r="E228" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="7" t="inlineStr">
+      <c r="A229" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B229" s="7" t="inlineStr">
+      <c r="B229" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-2</t>
         </is>
       </c>
-      <c r="C229" s="8">
+      <c r="C229" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FQ-2")</f>
         <v/>
       </c>
-      <c r="D229" s="9">
+      <c r="D229" s="12">
         <f>C229</f>
         <v/>
       </c>
-      <c r="E229" s="7" t="inlineStr">
+      <c r="E229" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="7" t="inlineStr">
+      <c r="A230" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B230" s="7" t="inlineStr">
+      <c r="B230" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-3</t>
         </is>
       </c>
-      <c r="C230" s="8">
+      <c r="C230" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FQ-3")</f>
         <v/>
       </c>
-      <c r="D230" s="9">
+      <c r="D230" s="12">
         <f>C230</f>
         <v/>
       </c>
-      <c r="E230" s="7" t="inlineStr">
+      <c r="E230" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="7" t="inlineStr">
+      <c r="A231" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B231" s="7" t="inlineStr">
+      <c r="B231" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-4</t>
         </is>
       </c>
-      <c r="C231" s="8">
+      <c r="C231" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FQ-4")</f>
         <v/>
       </c>
-      <c r="D231" s="9">
+      <c r="D231" s="12">
         <f>C231</f>
         <v/>
       </c>
-      <c r="E231" s="7" t="inlineStr">
+      <c r="E231" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="7" t="inlineStr">
+      <c r="A232" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B232" s="7" t="inlineStr">
+      <c r="B232" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-5</t>
         </is>
       </c>
-      <c r="C232" s="8">
+      <c r="C232" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FQ-5")</f>
         <v/>
       </c>
-      <c r="D232" s="9">
+      <c r="D232" s="12">
         <f>C232</f>
         <v/>
       </c>
-      <c r="E232" s="7" t="inlineStr">
+      <c r="E232" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="7" t="inlineStr">
+      <c r="A233" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B233" s="7" t="inlineStr">
+      <c r="B233" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-6</t>
         </is>
       </c>
-      <c r="C233" s="8">
+      <c r="C233" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FQ-6")</f>
         <v/>
       </c>
-      <c r="D233" s="9">
+      <c r="D233" s="12">
         <f>C233</f>
         <v/>
       </c>
-      <c r="E233" s="7" t="inlineStr">
+      <c r="E233" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="7" t="inlineStr">
+      <c r="A234" s="10" t="inlineStr">
         <is>
           <t>total_tax_expense</t>
         </is>
       </c>
-      <c r="B234" s="7" t="inlineStr">
+      <c r="B234" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-7</t>
         </is>
       </c>
-      <c r="C234" s="8">
+      <c r="C234" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_INC_TAX","IQ_FQ-7")</f>
         <v/>
       </c>
-      <c r="D234" s="9">
+      <c r="D234" s="12">
         <f>C234</f>
         <v/>
       </c>
-      <c r="E234" s="7" t="inlineStr">
+      <c r="E234" s="10" t="inlineStr">
         <is>
           <t>Income Tax Expense</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="6" t="inlineStr">
+      <c r="A235" s="9" t="inlineStr">
         <is>
           <t>BALANCE SHEET (Annual)</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="7" t="inlineStr">
+      <c r="A236" s="10" t="inlineStr">
         <is>
           <t>cash_and_marketable_securities</t>
         </is>
       </c>
-      <c r="B236" s="7" t="inlineStr">
+      <c r="B236" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C236" s="8">
+      <c r="C236" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CASH_EQUIV","IQ_FY-0")</f>
         <v/>
       </c>
-      <c r="D236" s="9">
+      <c r="D236" s="12">
         <f>C236</f>
         <v/>
       </c>
-      <c r="E236" s="7" t="inlineStr">
+      <c r="E236" s="10" t="inlineStr">
         <is>
           <t>Cash &amp; Equivalents</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="7" t="inlineStr">
+      <c r="A237" s="10" t="inlineStr">
         <is>
           <t>cash_and_marketable_securities</t>
         </is>
       </c>
-      <c r="B237" s="7" t="inlineStr">
+      <c r="B237" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C237" s="8">
+      <c r="C237" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CASH_EQUIV","IQ_FY-1")</f>
         <v/>
       </c>
-      <c r="D237" s="9">
+      <c r="D237" s="12">
         <f>C237</f>
         <v/>
       </c>
-      <c r="E237" s="7" t="inlineStr">
+      <c r="E237" s="10" t="inlineStr">
         <is>
           <t>Cash &amp; Equivalents</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="7" t="inlineStr">
+      <c r="A238" s="10" t="inlineStr">
         <is>
           <t>cash_and_marketable_securities</t>
         </is>
       </c>
-      <c r="B238" s="7" t="inlineStr">
+      <c r="B238" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C238" s="8">
+      <c r="C238" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CASH_EQUIV","IQ_FY-2")</f>
         <v/>
       </c>
-      <c r="D238" s="9">
+      <c r="D238" s="12">
         <f>C238</f>
         <v/>
       </c>
-      <c r="E238" s="7" t="inlineStr">
+      <c r="E238" s="10" t="inlineStr">
         <is>
           <t>Cash &amp; Equivalents</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="7" t="inlineStr">
+      <c r="A239" s="10" t="inlineStr">
         <is>
           <t>cash_and_marketable_securities</t>
         </is>
       </c>
-      <c r="B239" s="7" t="inlineStr">
+      <c r="B239" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C239" s="8">
+      <c r="C239" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CASH_EQUIV","IQ_FY-3")</f>
         <v/>
       </c>
-      <c r="D239" s="9">
+      <c r="D239" s="12">
         <f>C239</f>
         <v/>
       </c>
-      <c r="E239" s="7" t="inlineStr">
+      <c r="E239" s="10" t="inlineStr">
         <is>
           <t>Cash &amp; Equivalents</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="7" t="inlineStr">
+      <c r="A240" s="10" t="inlineStr">
         <is>
           <t>cash_and_marketable_securities</t>
         </is>
       </c>
-      <c r="B240" s="7" t="inlineStr">
+      <c r="B240" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C240" s="8">
+      <c r="C240" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CASH_EQUIV","IQ_FY-4")</f>
         <v/>
       </c>
-      <c r="D240" s="9">
+      <c r="D240" s="12">
         <f>C240</f>
         <v/>
       </c>
-      <c r="E240" s="7" t="inlineStr">
+      <c r="E240" s="10" t="inlineStr">
         <is>
           <t>Cash &amp; Equivalents</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="7" t="inlineStr">
+      <c r="A241" s="10" t="inlineStr">
         <is>
           <t>cash_and_marketable_securities</t>
         </is>
       </c>
-      <c r="B241" s="7" t="inlineStr">
+      <c r="B241" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C241" s="8">
+      <c r="C241" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CASH_EQUIV","IQ_FY-5")</f>
         <v/>
       </c>
-      <c r="D241" s="9">
+      <c r="D241" s="12">
         <f>C241</f>
         <v/>
       </c>
-      <c r="E241" s="7" t="inlineStr">
+      <c r="E241" s="10" t="inlineStr">
         <is>
           <t>Cash &amp; Equivalents</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="7" t="inlineStr">
+      <c r="A242" s="10" t="inlineStr">
         <is>
           <t>cash_and_marketable_securities</t>
         </is>
       </c>
-      <c r="B242" s="7" t="inlineStr">
+      <c r="B242" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C242" s="8">
+      <c r="C242" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CASH_EQUIV","IQ_FY-6")</f>
         <v/>
       </c>
-      <c r="D242" s="9">
+      <c r="D242" s="12">
         <f>C242</f>
         <v/>
       </c>
-      <c r="E242" s="7" t="inlineStr">
+      <c r="E242" s="10" t="inlineStr">
         <is>
           <t>Cash &amp; Equivalents</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="7" t="inlineStr">
+      <c r="A243" s="10" t="inlineStr">
         <is>
           <t>cash_and_marketable_securities</t>
         </is>
       </c>
-      <c r="B243" s="7" t="inlineStr">
+      <c r="B243" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C243" s="8">
+      <c r="C243" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CASH_EQUIV","IQ_FY-7")</f>
         <v/>
       </c>
-      <c r="D243" s="9">
+      <c r="D243" s="12">
         <f>C243</f>
         <v/>
       </c>
-      <c r="E243" s="7" t="inlineStr">
+      <c r="E243" s="10" t="inlineStr">
         <is>
           <t>Cash &amp; Equivalents</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="7" t="inlineStr">
+      <c r="A244" s="10" t="inlineStr">
         <is>
           <t>cash_and_marketable_securities</t>
         </is>
       </c>
-      <c r="B244" s="7" t="inlineStr">
+      <c r="B244" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C244" s="8">
+      <c r="C244" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CASH_EQUIV","IQ_FY-8")</f>
         <v/>
       </c>
-      <c r="D244" s="9">
+      <c r="D244" s="12">
         <f>C244</f>
         <v/>
       </c>
-      <c r="E244" s="7" t="inlineStr">
+      <c r="E244" s="10" t="inlineStr">
         <is>
           <t>Cash &amp; Equivalents</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="7" t="inlineStr">
+      <c r="A245" s="10" t="inlineStr">
         <is>
           <t>cash_and_marketable_securities</t>
         </is>
       </c>
-      <c r="B245" s="7" t="inlineStr">
+      <c r="B245" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C245" s="8">
+      <c r="C245" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CASH_EQUIV","IQ_FY-9")</f>
         <v/>
       </c>
-      <c r="D245" s="9">
+      <c r="D245" s="12">
         <f>C245</f>
         <v/>
       </c>
-      <c r="E245" s="7" t="inlineStr">
+      <c r="E245" s="10" t="inlineStr">
         <is>
           <t>Cash &amp; Equivalents</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="7" t="inlineStr">
+      <c r="A246" s="10" t="inlineStr">
         <is>
           <t>cash_and_marketable_securities</t>
         </is>
       </c>
-      <c r="B246" s="7" t="inlineStr">
+      <c r="B246" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C246" s="8">
+      <c r="C246" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CASH_EQUIV","IQ_FY-10")</f>
         <v/>
       </c>
-      <c r="D246" s="9">
+      <c r="D246" s="12">
         <f>C246</f>
         <v/>
       </c>
-      <c r="E246" s="7" t="inlineStr">
+      <c r="E246" s="10" t="inlineStr">
         <is>
           <t>Cash &amp; Equivalents</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="7" t="inlineStr">
+      <c r="A247" s="10" t="inlineStr">
         <is>
           <t>bv_equity</t>
         </is>
       </c>
-      <c r="B247" s="7" t="inlineStr">
+      <c r="B247" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C247" s="8">
+      <c r="C247" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_EQUITY","IQ_FY-0")</f>
         <v/>
       </c>
-      <c r="D247" s="9">
+      <c r="D247" s="12">
         <f>C247</f>
         <v/>
       </c>
-      <c r="E247" s="7" t="inlineStr">
+      <c r="E247" s="10" t="inlineStr">
         <is>
           <t>Total Stockholders' Equity</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="7" t="inlineStr">
+      <c r="A248" s="10" t="inlineStr">
         <is>
           <t>bv_equity</t>
         </is>
       </c>
-      <c r="B248" s="7" t="inlineStr">
+      <c r="B248" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C248" s="8">
+      <c r="C248" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_EQUITY","IQ_FY-1")</f>
         <v/>
       </c>
-      <c r="D248" s="9">
+      <c r="D248" s="12">
         <f>C248</f>
         <v/>
       </c>
-      <c r="E248" s="7" t="inlineStr">
+      <c r="E248" s="10" t="inlineStr">
         <is>
           <t>Total Stockholders' Equity</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="7" t="inlineStr">
+      <c r="A249" s="10" t="inlineStr">
         <is>
           <t>bv_equity</t>
         </is>
       </c>
-      <c r="B249" s="7" t="inlineStr">
+      <c r="B249" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C249" s="8">
+      <c r="C249" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_EQUITY","IQ_FY-2")</f>
         <v/>
       </c>
-      <c r="D249" s="9">
+      <c r="D249" s="12">
         <f>C249</f>
         <v/>
       </c>
-      <c r="E249" s="7" t="inlineStr">
+      <c r="E249" s="10" t="inlineStr">
         <is>
           <t>Total Stockholders' Equity</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="7" t="inlineStr">
+      <c r="A250" s="10" t="inlineStr">
         <is>
           <t>bv_equity</t>
         </is>
       </c>
-      <c r="B250" s="7" t="inlineStr">
+      <c r="B250" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C250" s="8">
+      <c r="C250" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_EQUITY","IQ_FY-3")</f>
         <v/>
       </c>
-      <c r="D250" s="9">
+      <c r="D250" s="12">
         <f>C250</f>
         <v/>
       </c>
-      <c r="E250" s="7" t="inlineStr">
+      <c r="E250" s="10" t="inlineStr">
         <is>
           <t>Total Stockholders' Equity</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="7" t="inlineStr">
+      <c r="A251" s="10" t="inlineStr">
         <is>
           <t>bv_equity</t>
         </is>
       </c>
-      <c r="B251" s="7" t="inlineStr">
+      <c r="B251" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C251" s="8">
+      <c r="C251" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_EQUITY","IQ_FY-4")</f>
         <v/>
       </c>
-      <c r="D251" s="9">
+      <c r="D251" s="12">
         <f>C251</f>
         <v/>
       </c>
-      <c r="E251" s="7" t="inlineStr">
+      <c r="E251" s="10" t="inlineStr">
         <is>
           <t>Total Stockholders' Equity</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="7" t="inlineStr">
+      <c r="A252" s="10" t="inlineStr">
         <is>
           <t>bv_equity</t>
         </is>
       </c>
-      <c r="B252" s="7" t="inlineStr">
+      <c r="B252" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C252" s="8">
+      <c r="C252" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_EQUITY","IQ_FY-5")</f>
         <v/>
       </c>
-      <c r="D252" s="9">
+      <c r="D252" s="12">
         <f>C252</f>
         <v/>
       </c>
-      <c r="E252" s="7" t="inlineStr">
+      <c r="E252" s="10" t="inlineStr">
         <is>
           <t>Total Stockholders' Equity</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="7" t="inlineStr">
+      <c r="A253" s="10" t="inlineStr">
         <is>
           <t>bv_equity</t>
         </is>
       </c>
-      <c r="B253" s="7" t="inlineStr">
+      <c r="B253" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C253" s="8">
+      <c r="C253" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_EQUITY","IQ_FY-6")</f>
         <v/>
       </c>
-      <c r="D253" s="9">
+      <c r="D253" s="12">
         <f>C253</f>
         <v/>
       </c>
-      <c r="E253" s="7" t="inlineStr">
+      <c r="E253" s="10" t="inlineStr">
         <is>
           <t>Total Stockholders' Equity</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="7" t="inlineStr">
+      <c r="A254" s="10" t="inlineStr">
         <is>
           <t>bv_equity</t>
         </is>
       </c>
-      <c r="B254" s="7" t="inlineStr">
+      <c r="B254" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C254" s="8">
+      <c r="C254" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_EQUITY","IQ_FY-7")</f>
         <v/>
       </c>
-      <c r="D254" s="9">
+      <c r="D254" s="12">
         <f>C254</f>
         <v/>
       </c>
-      <c r="E254" s="7" t="inlineStr">
+      <c r="E254" s="10" t="inlineStr">
         <is>
           <t>Total Stockholders' Equity</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="7" t="inlineStr">
+      <c r="A255" s="10" t="inlineStr">
         <is>
           <t>bv_equity</t>
         </is>
       </c>
-      <c r="B255" s="7" t="inlineStr">
+      <c r="B255" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C255" s="8">
+      <c r="C255" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_EQUITY","IQ_FY-8")</f>
         <v/>
       </c>
-      <c r="D255" s="9">
+      <c r="D255" s="12">
         <f>C255</f>
         <v/>
       </c>
-      <c r="E255" s="7" t="inlineStr">
+      <c r="E255" s="10" t="inlineStr">
         <is>
           <t>Total Stockholders' Equity</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="7" t="inlineStr">
+      <c r="A256" s="10" t="inlineStr">
         <is>
           <t>bv_equity</t>
         </is>
       </c>
-      <c r="B256" s="7" t="inlineStr">
+      <c r="B256" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C256" s="8">
+      <c r="C256" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_EQUITY","IQ_FY-9")</f>
         <v/>
       </c>
-      <c r="D256" s="9">
+      <c r="D256" s="12">
         <f>C256</f>
         <v/>
       </c>
-      <c r="E256" s="7" t="inlineStr">
+      <c r="E256" s="10" t="inlineStr">
         <is>
           <t>Total Stockholders' Equity</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="7" t="inlineStr">
+      <c r="A257" s="10" t="inlineStr">
         <is>
           <t>bv_equity</t>
         </is>
       </c>
-      <c r="B257" s="7" t="inlineStr">
+      <c r="B257" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C257" s="8">
+      <c r="C257" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_EQUITY","IQ_FY-10")</f>
         <v/>
       </c>
-      <c r="D257" s="9">
+      <c r="D257" s="12">
         <f>C257</f>
         <v/>
       </c>
-      <c r="E257" s="7" t="inlineStr">
+      <c r="E257" s="10" t="inlineStr">
         <is>
           <t>Total Stockholders' Equity</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="7" t="inlineStr">
+      <c r="A258" s="10" t="inlineStr">
         <is>
           <t>bv_debt</t>
         </is>
       </c>
-      <c r="B258" s="7" t="inlineStr">
+      <c r="B258" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C258" s="8">
+      <c r="C258" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_DEBT","IQ_FY-0")</f>
         <v/>
       </c>
-      <c r="D258" s="9">
+      <c r="D258" s="12">
         <f>C258</f>
         <v/>
       </c>
-      <c r="E258" s="7" t="inlineStr">
+      <c r="E258" s="10" t="inlineStr">
         <is>
           <t>Total Debt</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="7" t="inlineStr">
+      <c r="A259" s="10" t="inlineStr">
         <is>
           <t>bv_debt</t>
         </is>
       </c>
-      <c r="B259" s="7" t="inlineStr">
+      <c r="B259" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C259" s="8">
+      <c r="C259" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_DEBT","IQ_FY-1")</f>
         <v/>
       </c>
-      <c r="D259" s="9">
+      <c r="D259" s="12">
         <f>C259</f>
         <v/>
       </c>
-      <c r="E259" s="7" t="inlineStr">
+      <c r="E259" s="10" t="inlineStr">
         <is>
           <t>Total Debt</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="7" t="inlineStr">
+      <c r="A260" s="10" t="inlineStr">
         <is>
           <t>bv_debt</t>
         </is>
       </c>
-      <c r="B260" s="7" t="inlineStr">
+      <c r="B260" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C260" s="8">
+      <c r="C260" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_DEBT","IQ_FY-2")</f>
         <v/>
       </c>
-      <c r="D260" s="9">
+      <c r="D260" s="12">
         <f>C260</f>
         <v/>
       </c>
-      <c r="E260" s="7" t="inlineStr">
+      <c r="E260" s="10" t="inlineStr">
         <is>
           <t>Total Debt</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="7" t="inlineStr">
+      <c r="A261" s="10" t="inlineStr">
         <is>
           <t>bv_debt</t>
         </is>
       </c>
-      <c r="B261" s="7" t="inlineStr">
+      <c r="B261" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C261" s="8">
+      <c r="C261" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_DEBT","IQ_FY-3")</f>
         <v/>
       </c>
-      <c r="D261" s="9">
+      <c r="D261" s="12">
         <f>C261</f>
         <v/>
       </c>
-      <c r="E261" s="7" t="inlineStr">
+      <c r="E261" s="10" t="inlineStr">
         <is>
           <t>Total Debt</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="7" t="inlineStr">
+      <c r="A262" s="10" t="inlineStr">
         <is>
           <t>bv_debt</t>
         </is>
       </c>
-      <c r="B262" s="7" t="inlineStr">
+      <c r="B262" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C262" s="8">
+      <c r="C262" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_DEBT","IQ_FY-4")</f>
         <v/>
       </c>
-      <c r="D262" s="9">
+      <c r="D262" s="12">
         <f>C262</f>
         <v/>
       </c>
-      <c r="E262" s="7" t="inlineStr">
+      <c r="E262" s="10" t="inlineStr">
         <is>
           <t>Total Debt</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="7" t="inlineStr">
+      <c r="A263" s="10" t="inlineStr">
         <is>
           <t>bv_debt</t>
         </is>
       </c>
-      <c r="B263" s="7" t="inlineStr">
+      <c r="B263" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C263" s="8">
+      <c r="C263" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_DEBT","IQ_FY-5")</f>
         <v/>
       </c>
-      <c r="D263" s="9">
+      <c r="D263" s="12">
         <f>C263</f>
         <v/>
       </c>
-      <c r="E263" s="7" t="inlineStr">
+      <c r="E263" s="10" t="inlineStr">
         <is>
           <t>Total Debt</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="7" t="inlineStr">
+      <c r="A264" s="10" t="inlineStr">
         <is>
           <t>bv_debt</t>
         </is>
       </c>
-      <c r="B264" s="7" t="inlineStr">
+      <c r="B264" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C264" s="8">
+      <c r="C264" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_DEBT","IQ_FY-6")</f>
         <v/>
       </c>
-      <c r="D264" s="9">
+      <c r="D264" s="12">
         <f>C264</f>
         <v/>
       </c>
-      <c r="E264" s="7" t="inlineStr">
+      <c r="E264" s="10" t="inlineStr">
         <is>
           <t>Total Debt</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="7" t="inlineStr">
+      <c r="A265" s="10" t="inlineStr">
         <is>
           <t>bv_debt</t>
         </is>
       </c>
-      <c r="B265" s="7" t="inlineStr">
+      <c r="B265" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C265" s="8">
+      <c r="C265" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_DEBT","IQ_FY-7")</f>
         <v/>
       </c>
-      <c r="D265" s="9">
+      <c r="D265" s="12">
         <f>C265</f>
         <v/>
       </c>
-      <c r="E265" s="7" t="inlineStr">
+      <c r="E265" s="10" t="inlineStr">
         <is>
           <t>Total Debt</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="7" t="inlineStr">
+      <c r="A266" s="10" t="inlineStr">
         <is>
           <t>bv_debt</t>
         </is>
       </c>
-      <c r="B266" s="7" t="inlineStr">
+      <c r="B266" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C266" s="8">
+      <c r="C266" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_DEBT","IQ_FY-8")</f>
         <v/>
       </c>
-      <c r="D266" s="9">
+      <c r="D266" s="12">
         <f>C266</f>
         <v/>
       </c>
-      <c r="E266" s="7" t="inlineStr">
+      <c r="E266" s="10" t="inlineStr">
         <is>
           <t>Total Debt</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="7" t="inlineStr">
+      <c r="A267" s="10" t="inlineStr">
         <is>
           <t>bv_debt</t>
         </is>
       </c>
-      <c r="B267" s="7" t="inlineStr">
+      <c r="B267" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C267" s="8">
+      <c r="C267" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_DEBT","IQ_FY-9")</f>
         <v/>
       </c>
-      <c r="D267" s="9">
+      <c r="D267" s="12">
         <f>C267</f>
         <v/>
       </c>
-      <c r="E267" s="7" t="inlineStr">
+      <c r="E267" s="10" t="inlineStr">
         <is>
           <t>Total Debt</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="7" t="inlineStr">
+      <c r="A268" s="10" t="inlineStr">
         <is>
           <t>bv_debt</t>
         </is>
       </c>
-      <c r="B268" s="7" t="inlineStr">
+      <c r="B268" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C268" s="8">
+      <c r="C268" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_DEBT","IQ_FY-10")</f>
         <v/>
       </c>
-      <c r="D268" s="9">
+      <c r="D268" s="12">
         <f>C268</f>
         <v/>
       </c>
-      <c r="E268" s="7" t="inlineStr">
+      <c r="E268" s="10" t="inlineStr">
         <is>
           <t>Total Debt</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="7" t="inlineStr">
+      <c r="A269" s="10" t="inlineStr">
         <is>
           <t>shares_outstanding</t>
         </is>
       </c>
-      <c r="B269" s="7" t="inlineStr">
+      <c r="B269" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C269" s="8">
+      <c r="C269" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_OUTSTANDING_FILING_DATE","IQ_FY-0")</f>
         <v/>
       </c>
-      <c r="D269" s="9">
+      <c r="D269" s="12">
         <f>C269</f>
         <v/>
       </c>
-      <c r="E269" s="7" t="inlineStr">
+      <c r="E269" s="10" t="inlineStr">
         <is>
           <t>Total Shares Outstanding (Filing Date)</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="7" t="inlineStr">
+      <c r="A270" s="10" t="inlineStr">
         <is>
           <t>shares_outstanding</t>
         </is>
       </c>
-      <c r="B270" s="7" t="inlineStr">
+      <c r="B270" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C270" s="8">
+      <c r="C270" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_OUTSTANDING_FILING_DATE","IQ_FY-1")</f>
         <v/>
       </c>
-      <c r="D270" s="9">
+      <c r="D270" s="12">
         <f>C270</f>
         <v/>
       </c>
-      <c r="E270" s="7" t="inlineStr">
+      <c r="E270" s="10" t="inlineStr">
         <is>
           <t>Total Shares Outstanding (Filing Date)</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="7" t="inlineStr">
+      <c r="A271" s="10" t="inlineStr">
         <is>
           <t>shares_outstanding</t>
         </is>
       </c>
-      <c r="B271" s="7" t="inlineStr">
+      <c r="B271" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C271" s="8">
+      <c r="C271" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_OUTSTANDING_FILING_DATE","IQ_FY-2")</f>
         <v/>
       </c>
-      <c r="D271" s="9">
+      <c r="D271" s="12">
         <f>C271</f>
         <v/>
       </c>
-      <c r="E271" s="7" t="inlineStr">
+      <c r="E271" s="10" t="inlineStr">
         <is>
           <t>Total Shares Outstanding (Filing Date)</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="7" t="inlineStr">
+      <c r="A272" s="10" t="inlineStr">
         <is>
           <t>shares_outstanding</t>
         </is>
       </c>
-      <c r="B272" s="7" t="inlineStr">
+      <c r="B272" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C272" s="8">
+      <c r="C272" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_OUTSTANDING_FILING_DATE","IQ_FY-3")</f>
         <v/>
       </c>
-      <c r="D272" s="9">
+      <c r="D272" s="12">
         <f>C272</f>
         <v/>
       </c>
-      <c r="E272" s="7" t="inlineStr">
+      <c r="E272" s="10" t="inlineStr">
         <is>
           <t>Total Shares Outstanding (Filing Date)</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="7" t="inlineStr">
+      <c r="A273" s="10" t="inlineStr">
         <is>
           <t>shares_outstanding</t>
         </is>
       </c>
-      <c r="B273" s="7" t="inlineStr">
+      <c r="B273" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C273" s="8">
+      <c r="C273" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_OUTSTANDING_FILING_DATE","IQ_FY-4")</f>
         <v/>
       </c>
-      <c r="D273" s="9">
+      <c r="D273" s="12">
         <f>C273</f>
         <v/>
       </c>
-      <c r="E273" s="7" t="inlineStr">
+      <c r="E273" s="10" t="inlineStr">
         <is>
           <t>Total Shares Outstanding (Filing Date)</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="7" t="inlineStr">
+      <c r="A274" s="10" t="inlineStr">
         <is>
           <t>shares_outstanding</t>
         </is>
       </c>
-      <c r="B274" s="7" t="inlineStr">
+      <c r="B274" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C274" s="8">
+      <c r="C274" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_OUTSTANDING_FILING_DATE","IQ_FY-5")</f>
         <v/>
       </c>
-      <c r="D274" s="9">
+      <c r="D274" s="12">
         <f>C274</f>
         <v/>
       </c>
-      <c r="E274" s="7" t="inlineStr">
+      <c r="E274" s="10" t="inlineStr">
         <is>
           <t>Total Shares Outstanding (Filing Date)</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="7" t="inlineStr">
+      <c r="A275" s="10" t="inlineStr">
         <is>
           <t>shares_outstanding</t>
         </is>
       </c>
-      <c r="B275" s="7" t="inlineStr">
+      <c r="B275" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C275" s="8">
+      <c r="C275" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_OUTSTANDING_FILING_DATE","IQ_FY-6")</f>
         <v/>
       </c>
-      <c r="D275" s="9">
+      <c r="D275" s="12">
         <f>C275</f>
         <v/>
       </c>
-      <c r="E275" s="7" t="inlineStr">
+      <c r="E275" s="10" t="inlineStr">
         <is>
           <t>Total Shares Outstanding (Filing Date)</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="7" t="inlineStr">
+      <c r="A276" s="10" t="inlineStr">
         <is>
           <t>shares_outstanding</t>
         </is>
       </c>
-      <c r="B276" s="7" t="inlineStr">
+      <c r="B276" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C276" s="8">
+      <c r="C276" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_OUTSTANDING_FILING_DATE","IQ_FY-7")</f>
         <v/>
       </c>
-      <c r="D276" s="9">
+      <c r="D276" s="12">
         <f>C276</f>
         <v/>
       </c>
-      <c r="E276" s="7" t="inlineStr">
+      <c r="E276" s="10" t="inlineStr">
         <is>
           <t>Total Shares Outstanding (Filing Date)</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="7" t="inlineStr">
+      <c r="A277" s="10" t="inlineStr">
         <is>
           <t>shares_outstanding</t>
         </is>
       </c>
-      <c r="B277" s="7" t="inlineStr">
+      <c r="B277" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C277" s="8">
+      <c r="C277" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_OUTSTANDING_FILING_DATE","IQ_FY-8")</f>
         <v/>
       </c>
-      <c r="D277" s="9">
+      <c r="D277" s="12">
         <f>C277</f>
         <v/>
       </c>
-      <c r="E277" s="7" t="inlineStr">
+      <c r="E277" s="10" t="inlineStr">
         <is>
           <t>Total Shares Outstanding (Filing Date)</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="7" t="inlineStr">
+      <c r="A278" s="10" t="inlineStr">
         <is>
           <t>shares_outstanding</t>
         </is>
       </c>
-      <c r="B278" s="7" t="inlineStr">
+      <c r="B278" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C278" s="8">
+      <c r="C278" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_OUTSTANDING_FILING_DATE","IQ_FY-9")</f>
         <v/>
       </c>
-      <c r="D278" s="9">
+      <c r="D278" s="12">
         <f>C278</f>
         <v/>
       </c>
-      <c r="E278" s="7" t="inlineStr">
+      <c r="E278" s="10" t="inlineStr">
         <is>
           <t>Total Shares Outstanding (Filing Date)</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="7" t="inlineStr">
+      <c r="A279" s="10" t="inlineStr">
         <is>
           <t>shares_outstanding</t>
         </is>
       </c>
-      <c r="B279" s="7" t="inlineStr">
+      <c r="B279" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C279" s="8">
+      <c r="C279" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_OUTSTANDING_FILING_DATE","IQ_FY-10")</f>
         <v/>
       </c>
-      <c r="D279" s="9">
+      <c r="D279" s="12">
         <f>C279</f>
         <v/>
       </c>
-      <c r="E279" s="7" t="inlineStr">
+      <c r="E279" s="10" t="inlineStr">
         <is>
           <t>Total Shares Outstanding (Filing Date)</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="7" t="inlineStr">
+      <c r="A280" s="10" t="inlineStr">
         <is>
           <t>cross_holdings</t>
         </is>
       </c>
-      <c r="B280" s="7" t="inlineStr">
+      <c r="B280" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C280" s="8">
+      <c r="C280" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_LT_INVEST","IQ_FY-0")</f>
         <v/>
       </c>
-      <c r="D280" s="9">
+      <c r="D280" s="12">
         <f>C280</f>
         <v/>
       </c>
-      <c r="E280" s="7" t="inlineStr">
+      <c r="E280" s="10" t="inlineStr">
         <is>
           <t>Long-term Investments (Cross Holdings)</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="7" t="inlineStr">
+      <c r="A281" s="10" t="inlineStr">
         <is>
           <t>cross_holdings</t>
         </is>
       </c>
-      <c r="B281" s="7" t="inlineStr">
+      <c r="B281" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C281" s="8">
+      <c r="C281" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_LT_INVEST","IQ_FY-1")</f>
         <v/>
       </c>
-      <c r="D281" s="9">
+      <c r="D281" s="12">
         <f>C281</f>
         <v/>
       </c>
-      <c r="E281" s="7" t="inlineStr">
+      <c r="E281" s="10" t="inlineStr">
         <is>
           <t>Long-term Investments (Cross Holdings)</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="7" t="inlineStr">
+      <c r="A282" s="10" t="inlineStr">
         <is>
           <t>cross_holdings</t>
         </is>
       </c>
-      <c r="B282" s="7" t="inlineStr">
+      <c r="B282" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C282" s="8">
+      <c r="C282" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_LT_INVEST","IQ_FY-2")</f>
         <v/>
       </c>
-      <c r="D282" s="9">
+      <c r="D282" s="12">
         <f>C282</f>
         <v/>
       </c>
-      <c r="E282" s="7" t="inlineStr">
+      <c r="E282" s="10" t="inlineStr">
         <is>
           <t>Long-term Investments (Cross Holdings)</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="7" t="inlineStr">
+      <c r="A283" s="10" t="inlineStr">
         <is>
           <t>cross_holdings</t>
         </is>
       </c>
-      <c r="B283" s="7" t="inlineStr">
+      <c r="B283" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C283" s="8">
+      <c r="C283" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_LT_INVEST","IQ_FY-3")</f>
         <v/>
       </c>
-      <c r="D283" s="9">
+      <c r="D283" s="12">
         <f>C283</f>
         <v/>
       </c>
-      <c r="E283" s="7" t="inlineStr">
+      <c r="E283" s="10" t="inlineStr">
         <is>
           <t>Long-term Investments (Cross Holdings)</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="7" t="inlineStr">
+      <c r="A284" s="10" t="inlineStr">
         <is>
           <t>cross_holdings</t>
         </is>
       </c>
-      <c r="B284" s="7" t="inlineStr">
+      <c r="B284" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C284" s="8">
+      <c r="C284" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_LT_INVEST","IQ_FY-4")</f>
         <v/>
       </c>
-      <c r="D284" s="9">
+      <c r="D284" s="12">
         <f>C284</f>
         <v/>
       </c>
-      <c r="E284" s="7" t="inlineStr">
+      <c r="E284" s="10" t="inlineStr">
         <is>
           <t>Long-term Investments (Cross Holdings)</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="7" t="inlineStr">
+      <c r="A285" s="10" t="inlineStr">
         <is>
           <t>cross_holdings</t>
         </is>
       </c>
-      <c r="B285" s="7" t="inlineStr">
+      <c r="B285" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C285" s="8">
+      <c r="C285" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_LT_INVEST","IQ_FY-5")</f>
         <v/>
       </c>
-      <c r="D285" s="9">
+      <c r="D285" s="12">
         <f>C285</f>
         <v/>
       </c>
-      <c r="E285" s="7" t="inlineStr">
+      <c r="E285" s="10" t="inlineStr">
         <is>
           <t>Long-term Investments (Cross Holdings)</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="7" t="inlineStr">
+      <c r="A286" s="10" t="inlineStr">
         <is>
           <t>cross_holdings</t>
         </is>
       </c>
-      <c r="B286" s="7" t="inlineStr">
+      <c r="B286" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C286" s="8">
+      <c r="C286" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_LT_INVEST","IQ_FY-6")</f>
         <v/>
       </c>
-      <c r="D286" s="9">
+      <c r="D286" s="12">
         <f>C286</f>
         <v/>
       </c>
-      <c r="E286" s="7" t="inlineStr">
+      <c r="E286" s="10" t="inlineStr">
         <is>
           <t>Long-term Investments (Cross Holdings)</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="7" t="inlineStr">
+      <c r="A287" s="10" t="inlineStr">
         <is>
           <t>cross_holdings</t>
         </is>
       </c>
-      <c r="B287" s="7" t="inlineStr">
+      <c r="B287" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C287" s="8">
+      <c r="C287" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_LT_INVEST","IQ_FY-7")</f>
         <v/>
       </c>
-      <c r="D287" s="9">
+      <c r="D287" s="12">
         <f>C287</f>
         <v/>
       </c>
-      <c r="E287" s="7" t="inlineStr">
+      <c r="E287" s="10" t="inlineStr">
         <is>
           <t>Long-term Investments (Cross Holdings)</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="7" t="inlineStr">
+      <c r="A288" s="10" t="inlineStr">
         <is>
           <t>cross_holdings</t>
         </is>
       </c>
-      <c r="B288" s="7" t="inlineStr">
+      <c r="B288" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C288" s="8">
+      <c r="C288" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_LT_INVEST","IQ_FY-8")</f>
         <v/>
       </c>
-      <c r="D288" s="9">
+      <c r="D288" s="12">
         <f>C288</f>
         <v/>
       </c>
-      <c r="E288" s="7" t="inlineStr">
+      <c r="E288" s="10" t="inlineStr">
         <is>
           <t>Long-term Investments (Cross Holdings)</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="7" t="inlineStr">
+      <c r="A289" s="10" t="inlineStr">
         <is>
           <t>cross_holdings</t>
         </is>
       </c>
-      <c r="B289" s="7" t="inlineStr">
+      <c r="B289" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C289" s="8">
+      <c r="C289" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_LT_INVEST","IQ_FY-9")</f>
         <v/>
       </c>
-      <c r="D289" s="9">
+      <c r="D289" s="12">
         <f>C289</f>
         <v/>
       </c>
-      <c r="E289" s="7" t="inlineStr">
+      <c r="E289" s="10" t="inlineStr">
         <is>
           <t>Long-term Investments (Cross Holdings)</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="7" t="inlineStr">
+      <c r="A290" s="10" t="inlineStr">
         <is>
           <t>cross_holdings</t>
         </is>
       </c>
-      <c r="B290" s="7" t="inlineStr">
+      <c r="B290" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C290" s="8">
+      <c r="C290" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_LT_INVEST","IQ_FY-10")</f>
         <v/>
       </c>
-      <c r="D290" s="9">
+      <c r="D290" s="12">
         <f>C290</f>
         <v/>
       </c>
-      <c r="E290" s="7" t="inlineStr">
+      <c r="E290" s="10" t="inlineStr">
         <is>
           <t>Long-term Investments (Cross Holdings)</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="7" t="inlineStr">
+      <c r="A291" s="10" t="inlineStr">
         <is>
           <t>minority_interests</t>
         </is>
       </c>
-      <c r="B291" s="7" t="inlineStr">
+      <c r="B291" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C291" s="8">
+      <c r="C291" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_MINORITY_INTEREST","IQ_FY-0")</f>
         <v/>
       </c>
-      <c r="D291" s="9">
+      <c r="D291" s="12">
         <f>C291</f>
         <v/>
       </c>
-      <c r="E291" s="7" t="inlineStr">
+      <c r="E291" s="10" t="inlineStr">
         <is>
           <t>Minority Interests</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="7" t="inlineStr">
+      <c r="A292" s="10" t="inlineStr">
         <is>
           <t>minority_interests</t>
         </is>
       </c>
-      <c r="B292" s="7" t="inlineStr">
+      <c r="B292" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-1</t>
         </is>
       </c>
-      <c r="C292" s="8">
+      <c r="C292" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_MINORITY_INTEREST","IQ_FY-1")</f>
         <v/>
       </c>
-      <c r="D292" s="9">
+      <c r="D292" s="12">
         <f>C292</f>
         <v/>
       </c>
-      <c r="E292" s="7" t="inlineStr">
+      <c r="E292" s="10" t="inlineStr">
         <is>
           <t>Minority Interests</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="7" t="inlineStr">
+      <c r="A293" s="10" t="inlineStr">
         <is>
           <t>minority_interests</t>
         </is>
       </c>
-      <c r="B293" s="7" t="inlineStr">
+      <c r="B293" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-2</t>
         </is>
       </c>
-      <c r="C293" s="8">
+      <c r="C293" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_MINORITY_INTEREST","IQ_FY-2")</f>
         <v/>
       </c>
-      <c r="D293" s="9">
+      <c r="D293" s="12">
         <f>C293</f>
         <v/>
       </c>
-      <c r="E293" s="7" t="inlineStr">
+      <c r="E293" s="10" t="inlineStr">
         <is>
           <t>Minority Interests</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="7" t="inlineStr">
+      <c r="A294" s="10" t="inlineStr">
         <is>
           <t>minority_interests</t>
         </is>
       </c>
-      <c r="B294" s="7" t="inlineStr">
+      <c r="B294" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-3</t>
         </is>
       </c>
-      <c r="C294" s="8">
+      <c r="C294" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_MINORITY_INTEREST","IQ_FY-3")</f>
         <v/>
       </c>
-      <c r="D294" s="9">
+      <c r="D294" s="12">
         <f>C294</f>
         <v/>
       </c>
-      <c r="E294" s="7" t="inlineStr">
+      <c r="E294" s="10" t="inlineStr">
         <is>
           <t>Minority Interests</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="7" t="inlineStr">
+      <c r="A295" s="10" t="inlineStr">
         <is>
           <t>minority_interests</t>
         </is>
       </c>
-      <c r="B295" s="7" t="inlineStr">
+      <c r="B295" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-4</t>
         </is>
       </c>
-      <c r="C295" s="8">
+      <c r="C295" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_MINORITY_INTEREST","IQ_FY-4")</f>
         <v/>
       </c>
-      <c r="D295" s="9">
+      <c r="D295" s="12">
         <f>C295</f>
         <v/>
       </c>
-      <c r="E295" s="7" t="inlineStr">
+      <c r="E295" s="10" t="inlineStr">
         <is>
           <t>Minority Interests</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="7" t="inlineStr">
+      <c r="A296" s="10" t="inlineStr">
         <is>
           <t>minority_interests</t>
         </is>
       </c>
-      <c r="B296" s="7" t="inlineStr">
+      <c r="B296" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-5</t>
         </is>
       </c>
-      <c r="C296" s="8">
+      <c r="C296" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_MINORITY_INTEREST","IQ_FY-5")</f>
         <v/>
       </c>
-      <c r="D296" s="9">
+      <c r="D296" s="12">
         <f>C296</f>
         <v/>
       </c>
-      <c r="E296" s="7" t="inlineStr">
+      <c r="E296" s="10" t="inlineStr">
         <is>
           <t>Minority Interests</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="7" t="inlineStr">
+      <c r="A297" s="10" t="inlineStr">
         <is>
           <t>minority_interests</t>
         </is>
       </c>
-      <c r="B297" s="7" t="inlineStr">
+      <c r="B297" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-6</t>
         </is>
       </c>
-      <c r="C297" s="8">
+      <c r="C297" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_MINORITY_INTEREST","IQ_FY-6")</f>
         <v/>
       </c>
-      <c r="D297" s="9">
+      <c r="D297" s="12">
         <f>C297</f>
         <v/>
       </c>
-      <c r="E297" s="7" t="inlineStr">
+      <c r="E297" s="10" t="inlineStr">
         <is>
           <t>Minority Interests</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="7" t="inlineStr">
+      <c r="A298" s="10" t="inlineStr">
         <is>
           <t>minority_interests</t>
         </is>
       </c>
-      <c r="B298" s="7" t="inlineStr">
+      <c r="B298" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-7</t>
         </is>
       </c>
-      <c r="C298" s="8">
+      <c r="C298" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_MINORITY_INTEREST","IQ_FY-7")</f>
         <v/>
       </c>
-      <c r="D298" s="9">
+      <c r="D298" s="12">
         <f>C298</f>
         <v/>
       </c>
-      <c r="E298" s="7" t="inlineStr">
+      <c r="E298" s="10" t="inlineStr">
         <is>
           <t>Minority Interests</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="7" t="inlineStr">
+      <c r="A299" s="10" t="inlineStr">
         <is>
           <t>minority_interests</t>
         </is>
       </c>
-      <c r="B299" s="7" t="inlineStr">
+      <c r="B299" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-8</t>
         </is>
       </c>
-      <c r="C299" s="8">
+      <c r="C299" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_MINORITY_INTEREST","IQ_FY-8")</f>
         <v/>
       </c>
-      <c r="D299" s="9">
+      <c r="D299" s="12">
         <f>C299</f>
         <v/>
       </c>
-      <c r="E299" s="7" t="inlineStr">
+      <c r="E299" s="10" t="inlineStr">
         <is>
           <t>Minority Interests</t>
         </is>
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="7" t="inlineStr">
+      <c r="A300" s="10" t="inlineStr">
         <is>
           <t>minority_interests</t>
         </is>
       </c>
-      <c r="B300" s="7" t="inlineStr">
+      <c r="B300" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-9</t>
         </is>
       </c>
-      <c r="C300" s="8">
+      <c r="C300" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_MINORITY_INTEREST","IQ_FY-9")</f>
         <v/>
       </c>
-      <c r="D300" s="9">
+      <c r="D300" s="12">
         <f>C300</f>
         <v/>
       </c>
-      <c r="E300" s="7" t="inlineStr">
+      <c r="E300" s="10" t="inlineStr">
         <is>
           <t>Minority Interests</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="7" t="inlineStr">
+      <c r="A301" s="10" t="inlineStr">
         <is>
           <t>minority_interests</t>
         </is>
       </c>
-      <c r="B301" s="7" t="inlineStr">
+      <c r="B301" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-10</t>
         </is>
       </c>
-      <c r="C301" s="8">
+      <c r="C301" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_MINORITY_INTEREST","IQ_FY-10")</f>
         <v/>
       </c>
-      <c r="D301" s="9">
+      <c r="D301" s="12">
         <f>C301</f>
         <v/>
       </c>
-      <c r="E301" s="7" t="inlineStr">
+      <c r="E301" s="10" t="inlineStr">
         <is>
           <t>Minority Interests</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="6" t="inlineStr">
+      <c r="A302" s="9" t="inlineStr">
         <is>
           <t>BALANCE SHEET (Quarterly — latest 10-Q)</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="7" t="inlineStr">
+      <c r="A303" s="10" t="inlineStr">
         <is>
           <t>cash_and_marketable_securities</t>
         </is>
       </c>
-      <c r="B303" s="7" t="inlineStr">
+      <c r="B303" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C303" s="8">
+      <c r="C303" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CASH_EQUIV","IQ_FQ-0")</f>
         <v/>
       </c>
-      <c r="D303" s="9">
+      <c r="D303" s="12">
         <f>C303</f>
         <v/>
       </c>
-      <c r="E303" s="7" t="inlineStr">
+      <c r="E303" s="10" t="inlineStr">
         <is>
           <t>Cash &amp; Equivalents (latest quarter)</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="7" t="inlineStr">
+      <c r="A304" s="10" t="inlineStr">
         <is>
           <t>bv_equity</t>
         </is>
       </c>
-      <c r="B304" s="7" t="inlineStr">
+      <c r="B304" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C304" s="8">
+      <c r="C304" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_EQUITY","IQ_FQ-0")</f>
         <v/>
       </c>
-      <c r="D304" s="9">
+      <c r="D304" s="12">
         <f>C304</f>
         <v/>
       </c>
-      <c r="E304" s="7" t="inlineStr">
+      <c r="E304" s="10" t="inlineStr">
         <is>
           <t>Total Stockholders' Equity (latest quarter)</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="7" t="inlineStr">
+      <c r="A305" s="10" t="inlineStr">
         <is>
           <t>bv_debt</t>
         </is>
       </c>
-      <c r="B305" s="7" t="inlineStr">
+      <c r="B305" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C305" s="8">
+      <c r="C305" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_DEBT","IQ_FQ-0")</f>
         <v/>
       </c>
-      <c r="D305" s="9">
+      <c r="D305" s="12">
         <f>C305</f>
         <v/>
       </c>
-      <c r="E305" s="7" t="inlineStr">
+      <c r="E305" s="10" t="inlineStr">
         <is>
           <t>Total Debt (latest quarter)</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="7" t="inlineStr">
+      <c r="A306" s="10" t="inlineStr">
         <is>
           <t>shares_outstanding</t>
         </is>
       </c>
-      <c r="B306" s="7" t="inlineStr">
+      <c r="B306" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C306" s="8">
+      <c r="C306" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_TOTAL_OUTSTANDING_FILING_DATE","IQ_FQ-0")</f>
         <v/>
       </c>
-      <c r="D306" s="9">
+      <c r="D306" s="12">
         <f>C306</f>
         <v/>
       </c>
-      <c r="E306" s="7" t="inlineStr">
+      <c r="E306" s="10" t="inlineStr">
         <is>
           <t>Total Shares Outstanding (Filing Date) (latest quarter)</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="7" t="inlineStr">
+      <c r="A307" s="10" t="inlineStr">
         <is>
           <t>cross_holdings</t>
         </is>
       </c>
-      <c r="B307" s="7" t="inlineStr">
+      <c r="B307" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C307" s="8">
+      <c r="C307" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_LT_INVEST","IQ_FQ-0")</f>
         <v/>
       </c>
-      <c r="D307" s="9">
+      <c r="D307" s="12">
         <f>C307</f>
         <v/>
       </c>
-      <c r="E307" s="7" t="inlineStr">
+      <c r="E307" s="10" t="inlineStr">
         <is>
           <t>Long-term Investments (Cross Holdings) (latest quarter)</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="7" t="inlineStr">
+      <c r="A308" s="10" t="inlineStr">
         <is>
           <t>minority_interests</t>
         </is>
       </c>
-      <c r="B308" s="7" t="inlineStr">
+      <c r="B308" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C308" s="8">
+      <c r="C308" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_MINORITY_INTEREST","IQ_FQ-0")</f>
         <v/>
       </c>
-      <c r="D308" s="9">
+      <c r="D308" s="12">
         <f>C308</f>
         <v/>
       </c>
-      <c r="E308" s="7" t="inlineStr">
+      <c r="E308" s="10" t="inlineStr">
         <is>
           <t>Minority Interests (latest quarter)</t>
         </is>
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="6" t="inlineStr">
+      <c r="A309" s="9" t="inlineStr">
         <is>
           <t>MARKET DATA (Current)</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="7" t="inlineStr">
+      <c r="A310" s="10" t="inlineStr">
         <is>
           <t>stock_price</t>
         </is>
       </c>
-      <c r="B310" s="7" t="inlineStr">
+      <c r="B310" s="10" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="C310" s="8">
+      <c r="C310" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CLOSEPRICE")</f>
         <v/>
       </c>
-      <c r="D310" s="9">
+      <c r="D310" s="12">
         <f>C310</f>
         <v/>
       </c>
-      <c r="E310" s="7" t="inlineStr">
+      <c r="E310" s="10" t="inlineStr">
         <is>
           <t>Closing Stock Price (listing currency)</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="7" t="inlineStr">
+      <c r="A311" s="10" t="inlineStr">
         <is>
           <t>mv_equity</t>
         </is>
       </c>
-      <c r="B311" s="7" t="inlineStr">
+      <c r="B311" s="10" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="C311" s="8">
+      <c r="C311" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_MARKETCAP")</f>
         <v/>
       </c>
-      <c r="D311" s="9">
+      <c r="D311" s="12">
         <f>C311</f>
         <v/>
       </c>
-      <c r="E311" s="7" t="inlineStr">
+      <c r="E311" s="10" t="inlineStr">
         <is>
           <t>Market Capitalization (listing currency)</t>
         </is>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="7" t="inlineStr">
+      <c r="A312" s="10" t="inlineStr">
         <is>
           <t>stock_price_reporting</t>
         </is>
       </c>
-      <c r="B312" s="7" t="inlineStr">
+      <c r="B312" s="10" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="C312" s="8">
-        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CLOSEPRICE","","","&lt;FILING&gt;")</f>
-        <v/>
-      </c>
-      <c r="D312" s="9">
+      <c r="C312" s="11">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_CLOSEPRICE","","",$D$3)</f>
+        <v/>
+      </c>
+      <c r="D312" s="12">
         <f>C312</f>
         <v/>
       </c>
-      <c r="E312" s="7" t="inlineStr">
+      <c r="E312" s="10" t="inlineStr">
         <is>
           <t>Closing Stock Price (reporting currency)</t>
         </is>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="7" t="inlineStr">
+      <c r="A313" s="10" t="inlineStr">
         <is>
           <t>mv_equity_reporting</t>
         </is>
       </c>
-      <c r="B313" s="7" t="inlineStr">
+      <c r="B313" s="10" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="C313" s="8">
-        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_MARKETCAP","","","&lt;FILING&gt;")</f>
-        <v/>
-      </c>
-      <c r="D313" s="9">
+      <c r="C313" s="11">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_MARKETCAP","","",$D$3)</f>
+        <v/>
+      </c>
+      <c r="D313" s="12">
         <f>C313</f>
         <v/>
       </c>
-      <c r="E313" s="7" t="inlineStr">
+      <c r="E313" s="10" t="inlineStr">
         <is>
           <t>Market Capitalization (reporting currency)</t>
         </is>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="7" t="inlineStr">
+      <c r="A314" s="10" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="B314" s="7" t="inlineStr">
+      <c r="B314" s="10" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="C314" s="8">
+      <c r="C314" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_FILING_CURRENCY")</f>
         <v/>
       </c>
-      <c r="D314" s="9">
+      <c r="D314" s="12">
         <f>C314</f>
         <v/>
       </c>
-      <c r="E314" s="7" t="inlineStr">
+      <c r="E314" s="10" t="inlineStr">
         <is>
           <t>Filing/Reporting Currency</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="7" t="inlineStr">
+      <c r="A315" s="10" t="inlineStr">
         <is>
           <t>primary_exchange</t>
         </is>
       </c>
-      <c r="B315" s="7" t="inlineStr">
+      <c r="B315" s="10" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="C315" s="8">
+      <c r="C315" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EXCHANGE")</f>
         <v/>
       </c>
-      <c r="D315" s="9">
+      <c r="D315" s="12">
         <f>C315</f>
         <v/>
       </c>
-      <c r="E315" s="7" t="inlineStr">
+      <c r="E315" s="10" t="inlineStr">
         <is>
           <t>Primary Exchange Listing</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="7" t="inlineStr">
+      <c r="A316" s="10" t="inlineStr">
         <is>
           <t>effective_tax_rate_ciq</t>
         </is>
       </c>
-      <c r="B316" s="7" t="inlineStr">
+      <c r="B316" s="10" t="inlineStr">
         <is>
           <t>IQ_FY</t>
         </is>
       </c>
-      <c r="C316" s="8">
+      <c r="C316" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_EFFECT_TAX_RATE","IQ_FY")/100</f>
         <v/>
       </c>
-      <c r="D316" s="9">
+      <c r="D316" s="12">
         <f>C316</f>
         <v/>
       </c>
-      <c r="E316" s="7" t="inlineStr">
+      <c r="E316" s="10" t="inlineStr">
         <is>
           <t>Effective Tax Rate (CIQ, /100)</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="6" t="inlineStr">
+      <c r="A317" s="9" t="inlineStr">
         <is>
           <t>EMPLOYEE OPTIONS (Current)</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="7" t="inlineStr">
+      <c r="A318" s="10" t="inlineStr">
         <is>
           <t>options_outstanding</t>
         </is>
       </c>
-      <c r="B318" s="7" t="inlineStr">
+      <c r="B318" s="10" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="C318" s="8">
+      <c r="C318" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPTIONS_END_OS")</f>
         <v/>
       </c>
-      <c r="D318" s="9">
+      <c r="D318" s="12">
         <f>C318</f>
         <v/>
       </c>
-      <c r="E318" s="7" t="inlineStr">
+      <c r="E318" s="10" t="inlineStr">
         <is>
           <t>Options Outstanding (End of Period)</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="7" t="inlineStr">
+      <c r="A319" s="10" t="inlineStr">
         <is>
           <t>options_avg_strike</t>
         </is>
       </c>
-      <c r="B319" s="7" t="inlineStr">
+      <c r="B319" s="10" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="C319" s="8">
+      <c r="C319" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPTIONS_STRIKE_PRICE_OS")</f>
         <v/>
       </c>
-      <c r="D319" s="9">
+      <c r="D319" s="12">
         <f>C319</f>
         <v/>
       </c>
-      <c r="E319" s="7" t="inlineStr">
+      <c r="E319" s="10" t="inlineStr">
         <is>
           <t>Weighted Avg Strike Price (Outstanding)</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="7" t="inlineStr">
+      <c r="A320" s="10" t="inlineStr">
         <is>
           <t>options_avg_maturity</t>
         </is>
       </c>
-      <c r="B320" s="7" t="inlineStr">
+      <c r="B320" s="10" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="C320" s="8">
+      <c r="C320" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OPTIONS_AVG_LIFE")</f>
         <v/>
       </c>
-      <c r="D320" s="9">
+      <c r="D320" s="12">
         <f>C320</f>
         <v/>
       </c>
-      <c r="E320" s="7" t="inlineStr">
+      <c r="E320" s="10" t="inlineStr">
         <is>
           <t>Weighted Avg Remaining Life</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="6" t="inlineStr">
+      <c r="A321" s="9" t="inlineStr">
         <is>
           <t>OPERATING LEASE COMMITMENTS (Current)</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="7" t="inlineStr">
+      <c r="A322" s="10" t="inlineStr">
         <is>
           <t>lease_commitment_yr1</t>
         </is>
       </c>
-      <c r="B322" s="7" t="inlineStr">
+      <c r="B322" s="10" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="C322" s="8">
+      <c r="C322" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OL_COMM_CY")</f>
         <v/>
       </c>
-      <c r="D322" s="9">
+      <c r="D322" s="12">
         <f>C322</f>
         <v/>
       </c>
-      <c r="E322" s="7" t="inlineStr">
+      <c r="E322" s="10" t="inlineStr">
         <is>
           <t>Op Lease Commitment Year 1</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="7" t="inlineStr">
+      <c r="A323" s="10" t="inlineStr">
         <is>
           <t>lease_commitment_yr2</t>
         </is>
       </c>
-      <c r="B323" s="7" t="inlineStr">
+      <c r="B323" s="10" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="C323" s="8">
+      <c r="C323" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OL_COMM_CY1")</f>
         <v/>
       </c>
-      <c r="D323" s="9">
+      <c r="D323" s="12">
         <f>C323</f>
         <v/>
       </c>
-      <c r="E323" s="7" t="inlineStr">
+      <c r="E323" s="10" t="inlineStr">
         <is>
           <t>Op Lease Commitment Year 2</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="7" t="inlineStr">
+      <c r="A324" s="10" t="inlineStr">
         <is>
           <t>lease_commitment_yr3</t>
         </is>
       </c>
-      <c r="B324" s="7" t="inlineStr">
+      <c r="B324" s="10" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="C324" s="8">
+      <c r="C324" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OL_COMM_CY2")</f>
         <v/>
       </c>
-      <c r="D324" s="9">
+      <c r="D324" s="12">
         <f>C324</f>
         <v/>
       </c>
-      <c r="E324" s="7" t="inlineStr">
+      <c r="E324" s="10" t="inlineStr">
         <is>
           <t>Op Lease Commitment Year 3</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="7" t="inlineStr">
+      <c r="A325" s="10" t="inlineStr">
         <is>
           <t>lease_commitment_yr4</t>
         </is>
       </c>
-      <c r="B325" s="7" t="inlineStr">
+      <c r="B325" s="10" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="C325" s="8">
+      <c r="C325" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OL_COMM_CY3")</f>
         <v/>
       </c>
-      <c r="D325" s="9">
+      <c r="D325" s="12">
         <f>C325</f>
         <v/>
       </c>
-      <c r="E325" s="7" t="inlineStr">
+      <c r="E325" s="10" t="inlineStr">
         <is>
           <t>Op Lease Commitment Year 4</t>
         </is>
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="7" t="inlineStr">
+      <c r="A326" s="10" t="inlineStr">
         <is>
           <t>lease_commitment_yr5</t>
         </is>
       </c>
-      <c r="B326" s="7" t="inlineStr">
+      <c r="B326" s="10" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="C326" s="8">
+      <c r="C326" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OL_COMM_CY4")</f>
         <v/>
       </c>
-      <c r="D326" s="9">
+      <c r="D326" s="12">
         <f>C326</f>
         <v/>
       </c>
-      <c r="E326" s="7" t="inlineStr">
+      <c r="E326" s="10" t="inlineStr">
         <is>
           <t>Op Lease Commitment Year 5</t>
         </is>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="7" t="inlineStr">
+      <c r="A327" s="10" t="inlineStr">
         <is>
           <t>lease_commitment_beyond</t>
         </is>
       </c>
-      <c r="B327" s="7" t="inlineStr">
+      <c r="B327" s="10" t="inlineStr">
         <is>
           <t>current</t>
         </is>
       </c>
-      <c r="C327" s="8">
+      <c r="C327" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_OL_COMM_NEXT_FIVE")</f>
         <v/>
       </c>
-      <c r="D327" s="9">
+      <c r="D327" s="12">
         <f>C327</f>
         <v/>
       </c>
-      <c r="E327" s="7" t="inlineStr">
+      <c r="E327" s="10" t="inlineStr">
         <is>
           <t>Op Lease Commitment Beyond Year 5</t>
         </is>
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="6" t="inlineStr">
+      <c r="A328" s="9" t="inlineStr">
         <is>
           <t>PERIOD DATES</t>
         </is>
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="7" t="inlineStr">
+      <c r="A329" s="10" t="inlineStr">
         <is>
           <t>period_date_annual</t>
         </is>
       </c>
-      <c r="B329" s="7" t="inlineStr">
+      <c r="B329" s="10" t="inlineStr">
         <is>
           <t>IQ_FY-0</t>
         </is>
       </c>
-      <c r="C329" s="8">
+      <c r="C329" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_PERIODDATE","IQ_FY-0")</f>
         <v/>
       </c>
-      <c r="D329" s="9">
+      <c r="D329" s="12">
         <f>C329</f>
         <v/>
       </c>
-      <c r="E329" s="7" t="inlineStr">
+      <c r="E329" s="10" t="inlineStr">
         <is>
           <t>Most recent 10-K period end date</t>
         </is>
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="7" t="inlineStr">
+      <c r="A330" s="10" t="inlineStr">
         <is>
           <t>period_date_quarterly</t>
         </is>
       </c>
-      <c r="B330" s="7" t="inlineStr">
+      <c r="B330" s="10" t="inlineStr">
         <is>
           <t>IQ_FQ-0</t>
         </is>
       </c>
-      <c r="C330" s="8">
+      <c r="C330" s="11">
         <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_PERIODDATE","IQ_FQ-0")</f>
         <v/>
       </c>
-      <c r="D330" s="9">
+      <c r="D330" s="12">
         <f>C330</f>
         <v/>
       </c>
-      <c r="E330" s="7" t="inlineStr">
+      <c r="E330" s="10" t="inlineStr">
         <is>
           <t>Most recent 10-Q period end date</t>
         </is>

--- a/knowledge_base/ciq_fetches/CIQ_Fetch_Template.xlsx
+++ b/knowledge_base/ciq_fetches/CIQ_Fetch_Template.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E330"/>
+  <dimension ref="A1:E351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8549,10 +8549,518 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" s="6" t="inlineStr">
+        <is>
+          <t>GEOGRAPHIC REVENUE SEGMENTS (top 10 by revenue, latest FY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_name_1</t>
+        </is>
+      </c>
+      <c r="B332" s="7" t="inlineStr">
+        <is>
+          <t>rank 1</t>
+        </is>
+      </c>
+      <c r="C332" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_NAME_ABS","IQ_FY",,,,,,1)</f>
+        <v/>
+      </c>
+      <c r="D332" s="7">
+        <f>C332</f>
+        <v/>
+      </c>
+      <c r="E332" s="7" t="inlineStr">
+        <is>
+          <t>Segment name (rank 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_1</t>
+        </is>
+      </c>
+      <c r="B333" s="7" t="inlineStr">
+        <is>
+          <t>rank 1</t>
+        </is>
+      </c>
+      <c r="C333" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_REV_ABS","IQ_FY",,,,,,1)</f>
+        <v/>
+      </c>
+      <c r="D333" s="9">
+        <f>C333</f>
+        <v/>
+      </c>
+      <c r="E333" s="7" t="inlineStr">
+        <is>
+          <t>Segment revenue (rank 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_name_2</t>
+        </is>
+      </c>
+      <c r="B334" s="7" t="inlineStr">
+        <is>
+          <t>rank 2</t>
+        </is>
+      </c>
+      <c r="C334" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_NAME_ABS","IQ_FY",,,,,,2)</f>
+        <v/>
+      </c>
+      <c r="D334" s="7">
+        <f>C334</f>
+        <v/>
+      </c>
+      <c r="E334" s="7" t="inlineStr">
+        <is>
+          <t>Segment name (rank 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_2</t>
+        </is>
+      </c>
+      <c r="B335" s="7" t="inlineStr">
+        <is>
+          <t>rank 2</t>
+        </is>
+      </c>
+      <c r="C335" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_REV_ABS","IQ_FY",,,,,,2)</f>
+        <v/>
+      </c>
+      <c r="D335" s="9">
+        <f>C335</f>
+        <v/>
+      </c>
+      <c r="E335" s="7" t="inlineStr">
+        <is>
+          <t>Segment revenue (rank 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_name_3</t>
+        </is>
+      </c>
+      <c r="B336" s="7" t="inlineStr">
+        <is>
+          <t>rank 3</t>
+        </is>
+      </c>
+      <c r="C336" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_NAME_ABS","IQ_FY",,,,,,3)</f>
+        <v/>
+      </c>
+      <c r="D336" s="7">
+        <f>C336</f>
+        <v/>
+      </c>
+      <c r="E336" s="7" t="inlineStr">
+        <is>
+          <t>Segment name (rank 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_3</t>
+        </is>
+      </c>
+      <c r="B337" s="7" t="inlineStr">
+        <is>
+          <t>rank 3</t>
+        </is>
+      </c>
+      <c r="C337" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_REV_ABS","IQ_FY",,,,,,3)</f>
+        <v/>
+      </c>
+      <c r="D337" s="9">
+        <f>C337</f>
+        <v/>
+      </c>
+      <c r="E337" s="7" t="inlineStr">
+        <is>
+          <t>Segment revenue (rank 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_name_4</t>
+        </is>
+      </c>
+      <c r="B338" s="7" t="inlineStr">
+        <is>
+          <t>rank 4</t>
+        </is>
+      </c>
+      <c r="C338" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_NAME_ABS","IQ_FY",,,,,,4)</f>
+        <v/>
+      </c>
+      <c r="D338" s="7">
+        <f>C338</f>
+        <v/>
+      </c>
+      <c r="E338" s="7" t="inlineStr">
+        <is>
+          <t>Segment name (rank 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_4</t>
+        </is>
+      </c>
+      <c r="B339" s="7" t="inlineStr">
+        <is>
+          <t>rank 4</t>
+        </is>
+      </c>
+      <c r="C339" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_REV_ABS","IQ_FY",,,,,,4)</f>
+        <v/>
+      </c>
+      <c r="D339" s="9">
+        <f>C339</f>
+        <v/>
+      </c>
+      <c r="E339" s="7" t="inlineStr">
+        <is>
+          <t>Segment revenue (rank 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_name_5</t>
+        </is>
+      </c>
+      <c r="B340" s="7" t="inlineStr">
+        <is>
+          <t>rank 5</t>
+        </is>
+      </c>
+      <c r="C340" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_NAME_ABS","IQ_FY",,,,,,5)</f>
+        <v/>
+      </c>
+      <c r="D340" s="7">
+        <f>C340</f>
+        <v/>
+      </c>
+      <c r="E340" s="7" t="inlineStr">
+        <is>
+          <t>Segment name (rank 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_5</t>
+        </is>
+      </c>
+      <c r="B341" s="7" t="inlineStr">
+        <is>
+          <t>rank 5</t>
+        </is>
+      </c>
+      <c r="C341" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_REV_ABS","IQ_FY",,,,,,5)</f>
+        <v/>
+      </c>
+      <c r="D341" s="9">
+        <f>C341</f>
+        <v/>
+      </c>
+      <c r="E341" s="7" t="inlineStr">
+        <is>
+          <t>Segment revenue (rank 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_name_6</t>
+        </is>
+      </c>
+      <c r="B342" s="7" t="inlineStr">
+        <is>
+          <t>rank 6</t>
+        </is>
+      </c>
+      <c r="C342" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_NAME_ABS","IQ_FY",,,,,,6)</f>
+        <v/>
+      </c>
+      <c r="D342" s="7">
+        <f>C342</f>
+        <v/>
+      </c>
+      <c r="E342" s="7" t="inlineStr">
+        <is>
+          <t>Segment name (rank 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_6</t>
+        </is>
+      </c>
+      <c r="B343" s="7" t="inlineStr">
+        <is>
+          <t>rank 6</t>
+        </is>
+      </c>
+      <c r="C343" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_REV_ABS","IQ_FY",,,,,,6)</f>
+        <v/>
+      </c>
+      <c r="D343" s="9">
+        <f>C343</f>
+        <v/>
+      </c>
+      <c r="E343" s="7" t="inlineStr">
+        <is>
+          <t>Segment revenue (rank 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_name_7</t>
+        </is>
+      </c>
+      <c r="B344" s="7" t="inlineStr">
+        <is>
+          <t>rank 7</t>
+        </is>
+      </c>
+      <c r="C344" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_NAME_ABS","IQ_FY",,,,,,7)</f>
+        <v/>
+      </c>
+      <c r="D344" s="7">
+        <f>C344</f>
+        <v/>
+      </c>
+      <c r="E344" s="7" t="inlineStr">
+        <is>
+          <t>Segment name (rank 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_7</t>
+        </is>
+      </c>
+      <c r="B345" s="7" t="inlineStr">
+        <is>
+          <t>rank 7</t>
+        </is>
+      </c>
+      <c r="C345" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_REV_ABS","IQ_FY",,,,,,7)</f>
+        <v/>
+      </c>
+      <c r="D345" s="9">
+        <f>C345</f>
+        <v/>
+      </c>
+      <c r="E345" s="7" t="inlineStr">
+        <is>
+          <t>Segment revenue (rank 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_name_8</t>
+        </is>
+      </c>
+      <c r="B346" s="7" t="inlineStr">
+        <is>
+          <t>rank 8</t>
+        </is>
+      </c>
+      <c r="C346" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_NAME_ABS","IQ_FY",,,,,,8)</f>
+        <v/>
+      </c>
+      <c r="D346" s="7">
+        <f>C346</f>
+        <v/>
+      </c>
+      <c r="E346" s="7" t="inlineStr">
+        <is>
+          <t>Segment name (rank 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_8</t>
+        </is>
+      </c>
+      <c r="B347" s="7" t="inlineStr">
+        <is>
+          <t>rank 8</t>
+        </is>
+      </c>
+      <c r="C347" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_REV_ABS","IQ_FY",,,,,,8)</f>
+        <v/>
+      </c>
+      <c r="D347" s="9">
+        <f>C347</f>
+        <v/>
+      </c>
+      <c r="E347" s="7" t="inlineStr">
+        <is>
+          <t>Segment revenue (rank 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_name_9</t>
+        </is>
+      </c>
+      <c r="B348" s="7" t="inlineStr">
+        <is>
+          <t>rank 9</t>
+        </is>
+      </c>
+      <c r="C348" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_NAME_ABS","IQ_FY",,,,,,9)</f>
+        <v/>
+      </c>
+      <c r="D348" s="7">
+        <f>C348</f>
+        <v/>
+      </c>
+      <c r="E348" s="7" t="inlineStr">
+        <is>
+          <t>Segment name (rank 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_9</t>
+        </is>
+      </c>
+      <c r="B349" s="7" t="inlineStr">
+        <is>
+          <t>rank 9</t>
+        </is>
+      </c>
+      <c r="C349" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_REV_ABS","IQ_FY",,,,,,9)</f>
+        <v/>
+      </c>
+      <c r="D349" s="9">
+        <f>C349</f>
+        <v/>
+      </c>
+      <c r="E349" s="7" t="inlineStr">
+        <is>
+          <t>Segment revenue (rank 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_name_10</t>
+        </is>
+      </c>
+      <c r="B350" s="7" t="inlineStr">
+        <is>
+          <t>rank 10</t>
+        </is>
+      </c>
+      <c r="C350" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_NAME_ABS","IQ_FY",,,,,,10)</f>
+        <v/>
+      </c>
+      <c r="D350" s="7">
+        <f>C350</f>
+        <v/>
+      </c>
+      <c r="E350" s="7" t="inlineStr">
+        <is>
+          <t>Segment name (rank 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="7" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_10</t>
+        </is>
+      </c>
+      <c r="B351" s="7" t="inlineStr">
+        <is>
+          <t>rank 10</t>
+        </is>
+      </c>
+      <c r="C351" s="8">
+        <f>_xll.ciqfunctions.udf.CIQ($B$1,"IQ_GEO_SEG_REV_ABS","IQ_FY",,,,,,10)</f>
+        <v/>
+      </c>
+      <c r="D351" s="9">
+        <f>C351</f>
+        <v/>
+      </c>
+      <c r="E351" s="7" t="inlineStr">
+        <is>
+          <t>Segment revenue (rank 10)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A328:E328"/>
     <mergeCell ref="A302:E302"/>
+    <mergeCell ref="A331:E331"/>
     <mergeCell ref="A235:E235"/>
     <mergeCell ref="A138:E138"/>
     <mergeCell ref="A5:E5"/>
@@ -8570,7 +9078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D319"/>
+  <dimension ref="A1:D339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14955,6 +15463,406 @@
         </is>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>332</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>geo_seg_name_1</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>rank_1</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_NAME_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>333</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_1</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>rank_1</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_REV_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>334</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>geo_seg_name_2</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>rank_2</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_NAME_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>335</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_2</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>rank_2</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_REV_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>336</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>geo_seg_name_3</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>rank_3</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_NAME_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>337</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_3</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>rank_3</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_REV_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>338</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>geo_seg_name_4</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>rank_4</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_NAME_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>339</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_4</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>rank_4</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_REV_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>340</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>geo_seg_name_5</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>rank_5</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_NAME_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>341</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_5</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>rank_5</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_REV_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>342</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>geo_seg_name_6</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>rank_6</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_NAME_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>343</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_6</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>rank_6</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_REV_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>344</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>geo_seg_name_7</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>rank_7</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_NAME_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>345</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_7</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>rank_7</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_REV_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>346</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>geo_seg_name_8</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>rank_8</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_NAME_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>347</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_8</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>rank_8</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_REV_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>348</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>geo_seg_name_9</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>rank_9</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_NAME_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>349</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_9</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>rank_9</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_REV_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>350</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>geo_seg_name_10</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>rank_10</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_NAME_ABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>351</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>geo_seg_rev_10</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>rank_10</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>IQ_GEO_SEG_REV_ABS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
